--- a/Docs/Lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/Docs/Lab02/Lab02_BBT_TCs_Form.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28627"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB1C782F-89F7-4B11-A70B-9AC8A8E6CB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0CEC025-83EE-44C9-BB65-F1879B49C42A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -13,21 +13,10 @@
     <sheet name="F01.BVA" sheetId="3" r:id="rId3"/>
     <sheet name="BBT-TCs" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -74,7 +63,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="H18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+    <comment ref="H21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -98,7 +87,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
+    <comment ref="M21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -128,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="156">
   <si>
     <t>VVSS, Info Romana, 2024-2025</t>
   </si>
@@ -608,15 +597,9 @@
     <t>TC1_ECP</t>
   </si>
   <si>
-    <t>Director1, Director2</t>
-  </si>
-  <si>
     <t>TC3_ECP</t>
   </si>
   <si>
-    <t>Error message-Empty movie title</t>
-  </si>
-  <si>
     <t>TC5_ECP</t>
   </si>
   <si>
@@ -624,9 +607,6 @@
   </si>
   <si>
     <t>TC4_BVA</t>
-  </si>
-  <si>
-    <t>TC5_BVA</t>
   </si>
   <si>
     <t>Statistics</t>
@@ -688,12 +668,96 @@
   <si>
     <t>not yet</t>
   </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>inStock</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>partDynamicValue</t>
+  </si>
+  <si>
+    <t>TC2_ECP</t>
+  </si>
+  <si>
+    <t>TC4_ECP</t>
+  </si>
+  <si>
+    <t>TC6_ECP</t>
+  </si>
+  <si>
+    <t>"Parte_de_test"</t>
+  </si>
+  <si>
+    <t>"Firma_de_test"</t>
+  </si>
+  <si>
+    <t>2,3,3</t>
+  </si>
+  <si>
+    <t>2,3,4</t>
+  </si>
+  <si>
+    <t>2,3,5</t>
+  </si>
+  <si>
+    <t>2,3,8</t>
+  </si>
+  <si>
+    <t>2,3,9</t>
+  </si>
+  <si>
+    <t>2,3,10</t>
+  </si>
+  <si>
+    <t>2,3,11</t>
+  </si>
+  <si>
+    <t>2,3,12</t>
+  </si>
+  <si>
+    <t>part added</t>
+  </si>
+  <si>
+    <t>TC1_BVA</t>
+  </si>
+  <si>
+    <t>TC2_BVA</t>
+  </si>
+  <si>
+    <t>part shouldn't be added</t>
+  </si>
+  <si>
+    <t>"parte1"</t>
+  </si>
+  <si>
+    <t>"company_a"</t>
+  </si>
+  <si>
+    <t>"company_b"</t>
+  </si>
+  <si>
+    <t>TC7_ECP</t>
+  </si>
+  <si>
+    <t>DOUBLE_MAX</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -793,26 +857,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="8" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
@@ -912,6 +958,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1383,7 +1442,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1393,33 +1452,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1459,17 +1512,17 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1479,26 +1532,31 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1513,7 +1571,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1546,58 +1604,58 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1609,7 +1667,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1627,15 +1685,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1654,6 +1724,36 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1669,60 +1769,12 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1731,18 +1783,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2055,7 +2095,7 @@
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
   <dimension ref="A1:O26"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="22.5703125" customWidth="1"/>
     <col min="9" max="9" width="32.85546875" customWidth="1"/>
@@ -2064,27 +2104,27 @@
     <col min="14" max="14" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10">
-      <c r="C1" s="53" t="s">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="55"/>
-      <c r="H1" s="51" t="s">
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="54"/>
+      <c r="H1" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-    </row>
-    <row r="2" spans="2:10">
-      <c r="H2" s="56" t="s">
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+    </row>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="H2" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-    </row>
-    <row r="3" spans="2:10">
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
         <v>3</v>
@@ -2093,62 +2133,62 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="H4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="H5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="2:10">
-      <c r="B6" s="37"/>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="33"/>
       <c r="H6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="2:10" ht="14.45" customHeight="1"/>
-    <row r="8" spans="2:10">
-      <c r="B8" s="49" t="s">
+    <row r="7" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="45" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="2:10">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>12</v>
       </c>
@@ -2156,7 +2196,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>13</v>
       </c>
@@ -2164,7 +2204,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>14</v>
       </c>
@@ -2172,32 +2212,32 @@
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:15">
-      <c r="B18" s="49" t="s">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B18" s="45" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
-      <c r="C20" s="47" t="s">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C20" s="43" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>19</v>
       </c>
@@ -2214,7 +2254,7 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>20</v>
       </c>
@@ -2231,26 +2271,26 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" ht="14.45" customHeight="1">
-      <c r="A24" s="48"/>
-      <c r="B24" s="52" t="s">
+    <row r="24" spans="1:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="44"/>
+      <c r="B24" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="52"/>
-      <c r="G24" s="52"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="52"/>
-      <c r="J24" s="52"/>
-      <c r="K24" s="52"/>
-      <c r="L24" s="52"/>
-      <c r="M24" s="52"/>
-      <c r="N24" s="52"/>
-    </row>
-    <row r="26" spans="1:15">
-      <c r="C26" s="50"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="51"/>
+      <c r="K24" s="51"/>
+      <c r="L24" s="51"/>
+      <c r="M24" s="51"/>
+      <c r="N24" s="51"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C26" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2269,7 +2309,7 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:Q22"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="18.140625" bestFit="1" customWidth="1"/>
@@ -2286,125 +2326,125 @@
     <col min="17" max="17" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17">
-      <c r="B1" s="53" t="s">
+    <row r="1" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="55"/>
-    </row>
-    <row r="3" spans="2:17">
-      <c r="B3" s="77" t="s">
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="54"/>
+    </row>
+    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B3" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="79"/>
-    </row>
-    <row r="5" spans="2:17">
-      <c r="B5" s="80" t="s">
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="76"/>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B5" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="G5" s="81" t="s">
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="G5" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="81"/>
-      <c r="K5" s="81"/>
-      <c r="L5" s="81"/>
-      <c r="M5" s="81"/>
-      <c r="N5" s="81"/>
-      <c r="O5" s="81"/>
-      <c r="P5" s="81"/>
-      <c r="Q5" s="81"/>
-    </row>
-    <row r="6" spans="2:17">
-      <c r="B6" s="23" t="s">
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
+      <c r="K5" s="78"/>
+      <c r="L5" s="78"/>
+      <c r="M5" s="78"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B6" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="82" t="s">
+      <c r="G6" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="64" t="s">
+      <c r="H6" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="62" t="s">
+      <c r="I6" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="67"/>
-      <c r="O6" s="63"/>
-      <c r="P6" s="66" t="s">
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
+      <c r="L6" s="66"/>
+      <c r="M6" s="66"/>
+      <c r="N6" s="66"/>
+      <c r="O6" s="62"/>
+      <c r="P6" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="Q6" s="66"/>
-    </row>
-    <row r="7" spans="2:17">
+      <c r="Q6" s="65"/>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="74" t="s">
+      <c r="C7" s="71" t="s">
         <v>32</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="65"/>
-      <c r="I7" s="23" t="s">
+      <c r="G7" s="80"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="J7" s="23" t="s">
+      <c r="J7" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="K7" s="23" t="s">
+      <c r="K7" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="L7" s="23" t="s">
+      <c r="L7" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="23" t="s">
+      <c r="M7" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="N7" s="62" t="s">
+      <c r="N7" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="O7" s="63"/>
-      <c r="P7" s="62" t="s">
+      <c r="O7" s="62"/>
+      <c r="P7" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="Q7" s="63"/>
-    </row>
-    <row r="8" spans="2:17">
+      <c r="Q7" s="62"/>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="74"/>
+      <c r="C8" s="71"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="19">
         <v>1</v>
       </c>
       <c r="H8" s="2" t="s">
@@ -2425,29 +2465,29 @@
       <c r="M8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N8" s="58" t="s">
+      <c r="N8" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="O8" s="59" t="s">
+      <c r="O8" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="P8" s="58" t="s">
+      <c r="P8" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="Q8" s="59"/>
-    </row>
-    <row r="9" spans="2:17">
+      <c r="Q8" s="58"/>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="74" t="s">
+      <c r="C9" s="71" t="s">
         <v>49</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>49</v>
       </c>
       <c r="E9" s="4"/>
-      <c r="G9" s="23">
+      <c r="G9" s="19">
         <v>2</v>
       </c>
       <c r="H9" s="2" t="s">
@@ -2468,333 +2508,333 @@
       <c r="M9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N9" s="58" t="s">
+      <c r="N9" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="O9" s="59" t="s">
+      <c r="O9" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="P9" s="58" t="s">
+      <c r="P9" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="Q9" s="59"/>
-    </row>
-    <row r="10" spans="2:17">
+      <c r="Q9" s="58"/>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="74"/>
+      <c r="C10" s="71"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="32">
         <v>3</v>
       </c>
-      <c r="H10" s="14" t="s">
+      <c r="H10" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="I10" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="J10" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="11">
         <v>2012</v>
       </c>
-      <c r="L10" s="14" t="s">
+      <c r="L10" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="M10" s="14" t="s">
+      <c r="M10" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="N10" s="70" t="s">
+      <c r="N10" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="O10" s="71"/>
-      <c r="P10" s="70" t="s">
+      <c r="O10" s="70"/>
+      <c r="P10" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="Q10" s="71"/>
-    </row>
-    <row r="11" spans="2:17" ht="15" customHeight="1">
+      <c r="Q10" s="70"/>
+    </row>
+    <row r="11" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="74" t="s">
+      <c r="C11" s="71" t="s">
         <v>57</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E11" s="4"/>
-      <c r="G11" s="36">
+      <c r="G11" s="32">
         <v>4</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H11" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="J11" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="K11" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="L11" s="14" t="s">
+      <c r="L11" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="M11" s="14" t="s">
+      <c r="M11" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N11" s="70" t="s">
+      <c r="N11" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="O11" s="71"/>
-      <c r="P11" s="70" t="s">
+      <c r="O11" s="70"/>
+      <c r="P11" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="Q11" s="71"/>
-    </row>
-    <row r="12" spans="2:17">
+      <c r="Q11" s="70"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>6</v>
       </c>
-      <c r="C12" s="74"/>
+      <c r="C12" s="71"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="10">
         <v>5</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K12" s="9" t="s">
+      <c r="K12" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="L12" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="M12" s="9" t="s">
+      <c r="M12" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="N12" s="9" t="s">
+      <c r="N12" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="O12" s="9"/>
-      <c r="P12" s="72" t="s">
+      <c r="O12" s="6"/>
+      <c r="P12" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="Q12" s="73"/>
-    </row>
-    <row r="13" spans="2:17">
+      <c r="Q12" s="68"/>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="75" t="s">
+      <c r="C13" s="72" t="s">
         <v>63</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>63</v>
       </c>
       <c r="E13" s="4"/>
-      <c r="G13" s="13">
+      <c r="G13" s="10">
         <v>6</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="J13" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="K13" s="9" t="s">
+      <c r="K13" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="L13" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="M13" s="9" t="s">
+      <c r="M13" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="N13" s="72" t="s">
+      <c r="N13" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="O13" s="73"/>
-      <c r="P13" s="72" t="s">
+      <c r="O13" s="68"/>
+      <c r="P13" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="Q13" s="73"/>
-    </row>
-    <row r="14" spans="2:17">
+      <c r="Q13" s="68"/>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="4">
         <v>8</v>
       </c>
-      <c r="C14" s="76"/>
+      <c r="C14" s="73"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="15">
         <v>7</v>
       </c>
-      <c r="H14" s="18">
+      <c r="H14" s="14">
         <v>10</v>
       </c>
-      <c r="I14" s="18" t="s">
+      <c r="I14" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="J14" s="18" t="s">
+      <c r="J14" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="K14" s="18" t="s">
+      <c r="K14" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="L14" s="18" t="s">
+      <c r="L14" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="M14" s="18" t="s">
+      <c r="M14" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="N14" s="68" t="s">
+      <c r="N14" s="81" t="s">
         <v>65</v>
       </c>
-      <c r="O14" s="69"/>
-      <c r="P14" s="60"/>
-      <c r="Q14" s="61"/>
-    </row>
-    <row r="15" spans="2:17">
+      <c r="O14" s="82"/>
+      <c r="P14" s="59"/>
+      <c r="Q14" s="60"/>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="74" t="s">
+      <c r="C15" s="71" t="s">
         <v>50</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
-      <c r="G15" s="19">
+      <c r="G15" s="15">
         <v>8</v>
       </c>
-      <c r="H15" s="18" t="s">
+      <c r="H15" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="18"/>
-      <c r="M15" s="18"/>
-      <c r="N15" s="58"/>
-      <c r="O15" s="59"/>
-      <c r="P15" s="60"/>
-      <c r="Q15" s="61"/>
-    </row>
-    <row r="16" spans="2:17">
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="57"/>
+      <c r="O15" s="58"/>
+      <c r="P15" s="59"/>
+      <c r="Q15" s="60"/>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B16" s="4">
         <v>10</v>
       </c>
-      <c r="C16" s="74"/>
+      <c r="C16" s="71"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="18"/>
-      <c r="M16" s="18"/>
-      <c r="N16" s="58"/>
-      <c r="O16" s="59"/>
-      <c r="P16" s="60"/>
-      <c r="Q16" s="61"/>
-    </row>
-    <row r="17" spans="2:17">
+      <c r="G16" s="15"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="57"/>
+      <c r="O16" s="58"/>
+      <c r="P16" s="59"/>
+      <c r="Q16" s="60"/>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" s="4">
         <v>11</v>
       </c>
-      <c r="C17" s="74" t="s">
+      <c r="C17" s="71" t="s">
         <v>50</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="18"/>
-      <c r="N17" s="58"/>
-      <c r="O17" s="59"/>
-      <c r="P17" s="60"/>
-      <c r="Q17" s="61"/>
-    </row>
-    <row r="18" spans="2:17">
+      <c r="G17" s="15"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="58"/>
+      <c r="P17" s="59"/>
+      <c r="Q17" s="60"/>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18" s="4">
         <v>12</v>
       </c>
-      <c r="C18" s="74"/>
+      <c r="C18" s="71"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
-      <c r="M18" s="18"/>
-      <c r="N18" s="58"/>
-      <c r="O18" s="59"/>
-      <c r="P18" s="60"/>
-      <c r="Q18" s="61"/>
-    </row>
-    <row r="19" spans="2:17">
+      <c r="G18" s="15"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="57"/>
+      <c r="O18" s="58"/>
+      <c r="P18" s="59"/>
+      <c r="Q18" s="60"/>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="4">
         <v>13</v>
       </c>
-      <c r="C19" s="74" t="s">
+      <c r="C19" s="71" t="s">
         <v>50</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
-      <c r="G19" s="23"/>
+      <c r="G19" s="19"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
-      <c r="N19" s="58"/>
-      <c r="O19" s="59"/>
-      <c r="P19" s="60"/>
-      <c r="Q19" s="61"/>
-    </row>
-    <row r="20" spans="2:17">
+      <c r="N19" s="57"/>
+      <c r="O19" s="58"/>
+      <c r="P19" s="59"/>
+      <c r="Q19" s="60"/>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
         <v>14</v>
       </c>
-      <c r="C20" s="74"/>
+      <c r="C20" s="71"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
-    <row r="22" spans="2:17">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D22" t="s">
         <v>66</v>
       </c>
-      <c r="F22" s="57"/>
-      <c r="G22" s="57"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="41">
@@ -2850,7 +2890,7 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:R30"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
@@ -2870,47 +2910,47 @@
     <col min="18" max="18" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18">
-      <c r="B1" s="53" t="s">
+    <row r="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="55"/>
-    </row>
-    <row r="3" spans="2:18">
-      <c r="B3" s="77" t="s">
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="54"/>
+    </row>
+    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B3" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="79"/>
-    </row>
-    <row r="5" spans="2:18">
-      <c r="B5" s="90" t="s">
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="76"/>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B5" s="89" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="90"/>
-      <c r="D5" s="90"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="81" t="s">
+      <c r="G5" s="78" t="s">
         <v>68</v>
       </c>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="81"/>
-      <c r="K5" s="81"/>
-      <c r="L5" s="81"/>
-      <c r="M5" s="81"/>
-      <c r="N5" s="81"/>
-      <c r="O5" s="81"/>
-      <c r="P5" s="81"/>
-      <c r="Q5" s="81"/>
-      <c r="R5" s="81"/>
-    </row>
-    <row r="6" spans="2:18" ht="14.45" customHeight="1">
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
+      <c r="K5" s="78"/>
+      <c r="L5" s="78"/>
+      <c r="M5" s="78"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+    </row>
+    <row r="6" spans="2:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>69</v>
       </c>
@@ -2920,602 +2960,602 @@
       <c r="D6" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="10"/>
-      <c r="G6" s="82" t="s">
+      <c r="E6" s="7"/>
+      <c r="G6" s="79" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="82" t="s">
+      <c r="H6" s="79" t="s">
         <v>71</v>
       </c>
-      <c r="I6" s="82" t="s">
+      <c r="I6" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="J6" s="64" t="s">
+      <c r="J6" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="K6" s="86" t="s">
+      <c r="K6" s="85" t="s">
         <v>30</v>
       </c>
-      <c r="L6" s="87"/>
-      <c r="M6" s="87"/>
-      <c r="N6" s="87"/>
-      <c r="O6" s="87"/>
-      <c r="P6" s="88"/>
-      <c r="Q6" s="86" t="s">
+      <c r="L6" s="86"/>
+      <c r="M6" s="86"/>
+      <c r="N6" s="86"/>
+      <c r="O6" s="86"/>
+      <c r="P6" s="87"/>
+      <c r="Q6" s="85" t="s">
         <v>31</v>
       </c>
-      <c r="R6" s="88"/>
-    </row>
-    <row r="7" spans="2:18" ht="29.1">
-      <c r="B7" s="75">
+      <c r="R6" s="87"/>
+    </row>
+    <row r="7" spans="2:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="B7" s="72">
         <v>1</v>
       </c>
-      <c r="C7" s="92" t="s">
+      <c r="C7" s="91" t="s">
         <v>74</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="65"/>
-      <c r="K7" s="23" t="s">
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="L7" s="23" t="s">
+      <c r="L7" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="M7" s="35" t="s">
+      <c r="M7" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="N7" s="35" t="s">
+      <c r="N7" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="O7" s="23" t="s">
+      <c r="O7" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="P7" s="23" t="s">
+      <c r="P7" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="Q7" s="62" t="s">
+      <c r="Q7" s="61" t="s">
         <v>76</v>
       </c>
-      <c r="R7" s="63"/>
-    </row>
-    <row r="8" spans="2:18">
-      <c r="B8" s="91"/>
-      <c r="C8" s="93"/>
+      <c r="R7" s="62"/>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B8" s="90"/>
+      <c r="C8" s="92"/>
       <c r="D8" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="19">
         <v>1</v>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="13">
         <v>1</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="I8" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="J8" s="16"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
-      <c r="M8" s="34"/>
-      <c r="N8" s="34"/>
-      <c r="O8" s="34"/>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="84"/>
-      <c r="R8" s="85"/>
-    </row>
-    <row r="9" spans="2:18">
-      <c r="B9" s="91"/>
-      <c r="C9" s="93"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="83"/>
+      <c r="R8" s="84"/>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B9" s="90"/>
+      <c r="C9" s="92"/>
       <c r="D9" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="15">
         <v>2</v>
       </c>
-      <c r="H9" s="20">
+      <c r="H9" s="16">
         <v>2</v>
       </c>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21" t="s">
+      <c r="I9" s="17"/>
+      <c r="J9" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="K9" s="22" t="s">
+      <c r="K9" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="L9" s="18" t="s">
+      <c r="L9" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="M9" s="18" t="s">
+      <c r="M9" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18" t="s">
+      <c r="N9" s="14"/>
+      <c r="O9" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="P9" s="18" t="s">
+      <c r="P9" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="Q9" s="72" t="s">
+      <c r="Q9" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="R9" s="73"/>
-    </row>
-    <row r="10" spans="2:18">
-      <c r="B10" s="91"/>
-      <c r="C10" s="93"/>
+      <c r="R9" s="68"/>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B10" s="90"/>
+      <c r="C10" s="92"/>
       <c r="D10" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="19">
         <v>3</v>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="13">
         <v>3</v>
       </c>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="33" t="s">
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="L10" s="34" t="s">
+      <c r="L10" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="M10" s="34">
+      <c r="M10" s="30">
         <v>2010</v>
       </c>
-      <c r="N10" s="34" t="s">
+      <c r="N10" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="O10" s="34" t="s">
+      <c r="O10" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="P10" s="34" t="s">
+      <c r="P10" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="Q10" s="84" t="s">
+      <c r="Q10" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="R10" s="85"/>
-    </row>
-    <row r="11" spans="2:18">
-      <c r="B11" s="91"/>
-      <c r="C11" s="93"/>
+      <c r="R10" s="84"/>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B11" s="90"/>
+      <c r="C11" s="92"/>
       <c r="D11" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="19">
         <v>4</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="13">
         <v>4</v>
       </c>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="33" t="s">
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="L11" s="34" t="s">
+      <c r="L11" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="M11" s="34">
+      <c r="M11" s="30">
         <v>2010</v>
       </c>
-      <c r="N11" s="34" t="s">
+      <c r="N11" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="O11" s="34" t="s">
+      <c r="O11" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="P11" s="34" t="s">
+      <c r="P11" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="Q11" s="84" t="s">
+      <c r="Q11" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="R11" s="85"/>
-    </row>
-    <row r="12" spans="2:18">
-      <c r="B12" s="76"/>
-      <c r="C12" s="94"/>
+      <c r="R11" s="84"/>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B12" s="73"/>
+      <c r="C12" s="93"/>
       <c r="D12" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="19">
         <v>5</v>
       </c>
-      <c r="H12" s="17">
+      <c r="H12" s="13">
         <v>5</v>
       </c>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="33" t="s">
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="L12" s="34" t="s">
+      <c r="L12" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="M12" s="34">
+      <c r="M12" s="30">
         <v>2010</v>
       </c>
-      <c r="N12" s="34" t="s">
+      <c r="N12" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="O12" s="34" t="s">
+      <c r="O12" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="P12" s="34" t="s">
+      <c r="P12" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="Q12" s="84" t="s">
+      <c r="Q12" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="R12" s="85"/>
-    </row>
-    <row r="13" spans="2:18">
-      <c r="B13" s="75">
+      <c r="R12" s="84"/>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B13" s="72">
         <v>2</v>
       </c>
-      <c r="C13" s="75" t="s">
+      <c r="C13" s="72" t="s">
         <v>89</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="15">
         <v>6</v>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="16">
         <v>6</v>
       </c>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21" t="s">
+      <c r="I13" s="17"/>
+      <c r="J13" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="K13" s="22" t="s">
+      <c r="K13" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="L13" s="18" t="s">
+      <c r="L13" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="M13" s="18">
+      <c r="M13" s="14">
         <v>2010</v>
       </c>
-      <c r="N13" s="18" t="s">
+      <c r="N13" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="O13" s="18" t="s">
+      <c r="O13" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="P13" s="18" t="s">
+      <c r="P13" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="Q13" s="72" t="s">
+      <c r="Q13" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="R13" s="73"/>
-    </row>
-    <row r="14" spans="2:18">
-      <c r="B14" s="91"/>
-      <c r="C14" s="91"/>
+      <c r="R13" s="68"/>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B14" s="90"/>
+      <c r="C14" s="90"/>
       <c r="D14" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="19">
         <v>7</v>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="13">
         <v>7</v>
       </c>
-      <c r="I14" s="16" t="s">
+      <c r="I14" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="J14" s="16" t="s">
+      <c r="J14" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="K14" s="34"/>
-      <c r="L14" s="34"/>
-      <c r="M14" s="34"/>
-      <c r="N14" s="34"/>
-      <c r="O14" s="34"/>
-      <c r="P14" s="34"/>
-      <c r="Q14" s="84"/>
-      <c r="R14" s="85"/>
-    </row>
-    <row r="15" spans="2:18">
-      <c r="B15" s="91"/>
-      <c r="C15" s="91"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="30"/>
+      <c r="P14" s="30"/>
+      <c r="Q14" s="83"/>
+      <c r="R14" s="84"/>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B15" s="90"/>
+      <c r="C15" s="90"/>
       <c r="D15" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="19">
         <v>8</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="13">
         <v>8</v>
       </c>
-      <c r="I15" s="16" t="s">
+      <c r="I15" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="J15" s="16" t="s">
+      <c r="J15" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="84"/>
-      <c r="R15" s="85"/>
-    </row>
-    <row r="16" spans="2:18">
-      <c r="B16" s="91"/>
-      <c r="C16" s="91"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="30"/>
+      <c r="O15" s="30"/>
+      <c r="P15" s="30"/>
+      <c r="Q15" s="83"/>
+      <c r="R15" s="84"/>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B16" s="90"/>
+      <c r="C16" s="90"/>
       <c r="D16" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="19">
         <v>9</v>
       </c>
-      <c r="H16" s="17"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="34"/>
-      <c r="M16" s="34"/>
-      <c r="N16" s="34"/>
-      <c r="O16" s="34"/>
-      <c r="P16" s="34"/>
-      <c r="Q16" s="84"/>
-      <c r="R16" s="85"/>
-    </row>
-    <row r="17" spans="2:18">
-      <c r="B17" s="91"/>
-      <c r="C17" s="91"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="30"/>
+      <c r="P16" s="30"/>
+      <c r="Q16" s="83"/>
+      <c r="R16" s="84"/>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B17" s="90"/>
+      <c r="C17" s="90"/>
       <c r="D17" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="19">
         <v>10</v>
       </c>
-      <c r="H17" s="17"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="34"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="34"/>
-      <c r="O17" s="34"/>
-      <c r="P17" s="34"/>
-      <c r="Q17" s="84"/>
-      <c r="R17" s="85"/>
-    </row>
-    <row r="18" spans="2:18">
-      <c r="B18" s="76"/>
-      <c r="C18" s="76"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="30"/>
+      <c r="L17" s="30"/>
+      <c r="M17" s="30"/>
+      <c r="N17" s="30"/>
+      <c r="O17" s="30"/>
+      <c r="P17" s="30"/>
+      <c r="Q17" s="83"/>
+      <c r="R17" s="84"/>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B18" s="73"/>
+      <c r="C18" s="73"/>
       <c r="D18" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G18" s="23">
+      <c r="G18" s="19">
         <v>11</v>
       </c>
-      <c r="H18" s="17"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="34"/>
-      <c r="L18" s="34"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="34"/>
-      <c r="O18" s="34"/>
-      <c r="P18" s="34"/>
-      <c r="Q18" s="84"/>
-      <c r="R18" s="85"/>
-    </row>
-    <row r="19" spans="2:18">
-      <c r="B19" s="75">
+      <c r="H18" s="13"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="30"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="30"/>
+      <c r="P18" s="30"/>
+      <c r="Q18" s="83"/>
+      <c r="R18" s="84"/>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B19" s="72">
         <v>3</v>
       </c>
-      <c r="C19" s="92" t="s">
+      <c r="C19" s="91" t="s">
         <v>97</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="19">
         <v>12</v>
       </c>
-      <c r="H19" s="17"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="34"/>
-      <c r="L19" s="34"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="34"/>
-      <c r="O19" s="34"/>
-      <c r="P19" s="34"/>
-      <c r="Q19" s="84"/>
-      <c r="R19" s="85"/>
-    </row>
-    <row r="20" spans="2:18">
-      <c r="B20" s="91"/>
-      <c r="C20" s="93"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="30"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="30"/>
+      <c r="P19" s="30"/>
+      <c r="Q19" s="83"/>
+      <c r="R19" s="84"/>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B20" s="90"/>
+      <c r="C20" s="92"/>
       <c r="D20" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="G20" s="23">
+      <c r="G20" s="19">
         <v>13</v>
       </c>
-      <c r="H20" s="17"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="34"/>
-      <c r="P20" s="34"/>
-      <c r="Q20" s="84"/>
-      <c r="R20" s="85"/>
-    </row>
-    <row r="21" spans="2:18">
-      <c r="B21" s="91"/>
-      <c r="C21" s="93"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="83"/>
+      <c r="R20" s="84"/>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B21" s="90"/>
+      <c r="C21" s="92"/>
       <c r="D21" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="19">
         <v>14</v>
       </c>
-      <c r="H21" s="17"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="34"/>
-      <c r="M21" s="34"/>
-      <c r="N21" s="34"/>
-      <c r="O21" s="34"/>
-      <c r="P21" s="34"/>
-      <c r="Q21" s="84"/>
-      <c r="R21" s="85"/>
-    </row>
-    <row r="22" spans="2:18">
-      <c r="B22" s="91"/>
-      <c r="C22" s="93"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="30"/>
+      <c r="P21" s="30"/>
+      <c r="Q21" s="83"/>
+      <c r="R21" s="84"/>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B22" s="90"/>
+      <c r="C22" s="92"/>
       <c r="D22" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G22" s="23">
+      <c r="G22" s="19">
         <v>15</v>
       </c>
-      <c r="H22" s="17"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="34"/>
-      <c r="M22" s="34"/>
-      <c r="N22" s="34"/>
-      <c r="O22" s="34"/>
-      <c r="P22" s="34"/>
-      <c r="Q22" s="84"/>
-      <c r="R22" s="85"/>
-    </row>
-    <row r="23" spans="2:18">
-      <c r="B23" s="91"/>
-      <c r="C23" s="93"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="30"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="30"/>
+      <c r="P22" s="30"/>
+      <c r="Q22" s="83"/>
+      <c r="R22" s="84"/>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B23" s="90"/>
+      <c r="C23" s="92"/>
       <c r="D23" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="G23" s="23">
+      <c r="G23" s="19">
         <v>16</v>
       </c>
-      <c r="H23" s="17"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="34"/>
-      <c r="L23" s="34"/>
-      <c r="M23" s="34"/>
-      <c r="N23" s="34"/>
-      <c r="O23" s="34"/>
-      <c r="P23" s="34"/>
-      <c r="Q23" s="84"/>
-      <c r="R23" s="85"/>
-    </row>
-    <row r="24" spans="2:18">
-      <c r="B24" s="76"/>
-      <c r="C24" s="94"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
+      <c r="Q23" s="83"/>
+      <c r="R23" s="84"/>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B24" s="73"/>
+      <c r="C24" s="93"/>
       <c r="D24" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="G24" s="23">
+      <c r="G24" s="19">
         <v>17</v>
       </c>
-      <c r="H24" s="17"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="34"/>
-      <c r="L24" s="34"/>
-      <c r="M24" s="34"/>
-      <c r="N24" s="34"/>
-      <c r="O24" s="34"/>
-      <c r="P24" s="34"/>
-      <c r="Q24" s="84"/>
-      <c r="R24" s="85"/>
-    </row>
-    <row r="25" spans="2:18">
-      <c r="B25" s="75">
+      <c r="H24" s="13"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+      <c r="M24" s="30"/>
+      <c r="N24" s="30"/>
+      <c r="O24" s="30"/>
+      <c r="P24" s="30"/>
+      <c r="Q24" s="83"/>
+      <c r="R24" s="84"/>
+    </row>
+    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B25" s="72">
         <v>4</v>
       </c>
-      <c r="C25" s="92" t="s">
+      <c r="C25" s="91" t="s">
         <v>50</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G25" s="23">
+      <c r="G25" s="19">
         <v>18</v>
       </c>
-      <c r="H25" s="17"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="34"/>
-      <c r="L25" s="34"/>
-      <c r="M25" s="34"/>
-      <c r="N25" s="34"/>
-      <c r="O25" s="34"/>
-      <c r="P25" s="34"/>
-      <c r="Q25" s="84"/>
-      <c r="R25" s="85"/>
-    </row>
-    <row r="26" spans="2:18">
-      <c r="B26" s="91"/>
-      <c r="C26" s="93"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="30"/>
+      <c r="P25" s="30"/>
+      <c r="Q25" s="83"/>
+      <c r="R25" s="84"/>
+    </row>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B26" s="90"/>
+      <c r="C26" s="92"/>
       <c r="D26" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="2:18">
-      <c r="B27" s="91"/>
-      <c r="C27" s="93"/>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B27" s="90"/>
+      <c r="C27" s="92"/>
       <c r="D27" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="2:18">
-      <c r="B28" s="91"/>
-      <c r="C28" s="93"/>
+    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B28" s="90"/>
+      <c r="C28" s="92"/>
       <c r="D28" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G28" s="57"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="89"/>
-      <c r="K28" s="89"/>
-      <c r="L28" s="89"/>
-      <c r="M28" s="89"/>
-      <c r="N28" s="43"/>
-    </row>
-    <row r="29" spans="2:18">
-      <c r="B29" s="91"/>
-      <c r="C29" s="93"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="88"/>
+      <c r="J28" s="88"/>
+      <c r="K28" s="88"/>
+      <c r="L28" s="88"/>
+      <c r="M28" s="88"/>
+      <c r="N28" s="39"/>
+    </row>
+    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B29" s="90"/>
+      <c r="C29" s="92"/>
       <c r="D29" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I29" s="95"/>
-      <c r="J29" s="95"/>
-      <c r="K29" s="95"/>
-      <c r="L29" s="95"/>
-      <c r="M29" s="95"/>
-      <c r="N29" s="44"/>
-    </row>
-    <row r="30" spans="2:18">
-      <c r="B30" s="76"/>
-      <c r="C30" s="94"/>
+      <c r="I29" s="94"/>
+      <c r="J29" s="94"/>
+      <c r="K29" s="94"/>
+      <c r="L29" s="94"/>
+      <c r="M29" s="94"/>
+      <c r="N29" s="40"/>
+    </row>
+    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B30" s="73"/>
+      <c r="C30" s="93"/>
       <c r="D30" s="2" t="s">
         <v>50</v>
       </c>
@@ -3574,612 +3614,740 @@
   <sheetPr>
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="B1:P21"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="B1:P24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" customWidth="1"/>
     <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.5703125" customWidth="1"/>
     <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.85546875" customWidth="1"/>
     <col min="13" max="13" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.85546875" customWidth="1"/>
+    <col min="14" max="14" width="21.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14">
-      <c r="B1" s="53" t="s">
+    <row r="1" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="55"/>
-    </row>
-    <row r="3" spans="2:14">
-      <c r="B3" s="134" t="s">
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="54"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B3" s="127" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="134"/>
-      <c r="D3" s="134"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="134"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="134"/>
-      <c r="I3" s="134"/>
-      <c r="J3" s="134"/>
-      <c r="K3" s="134"/>
-      <c r="L3" s="134"/>
-      <c r="M3" s="134"/>
-      <c r="N3" s="134"/>
-    </row>
-    <row r="4" spans="2:14">
-      <c r="B4" s="82" t="s">
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="127"/>
+      <c r="M3" s="127"/>
+      <c r="N3" s="127"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B4" s="79" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="128" t="s">
+      <c r="C4" s="125" t="s">
         <v>106</v>
       </c>
-      <c r="D4" s="113" t="s">
+      <c r="D4" s="111" t="s">
         <v>107</v>
       </c>
-      <c r="E4" s="64" t="s">
+      <c r="E4" s="63" t="s">
         <v>108</v>
       </c>
-      <c r="F4" s="62" t="s">
+      <c r="F4" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="63"/>
-      <c r="M4" s="66" t="s">
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="66"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="N4" s="66"/>
-    </row>
-    <row r="5" spans="2:14" ht="15" thickBot="1">
-      <c r="B5" s="112"/>
-      <c r="C5" s="129"/>
-      <c r="D5" s="114"/>
-      <c r="E5" s="127"/>
-      <c r="F5" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="K5" s="121" t="s">
-        <v>38</v>
-      </c>
-      <c r="L5" s="122"/>
-      <c r="M5" s="26" t="s">
+      <c r="N4" s="65"/>
+    </row>
+    <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="110"/>
+      <c r="C5" s="126"/>
+      <c r="D5" s="112"/>
+      <c r="E5" s="124"/>
+      <c r="F5" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="H5" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="I5" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="K5" s="122" t="s">
+        <v>133</v>
+      </c>
+      <c r="L5" s="123"/>
+      <c r="M5" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="N5" s="26" t="s">
+      <c r="N5" s="22" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="15" thickTop="1">
-      <c r="B6" s="24">
+    <row r="6" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="20">
         <v>1</v>
       </c>
-      <c r="C6" s="110" t="s">
+      <c r="C6" s="108" t="s">
         <v>110</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="H6" s="29">
-        <v>2010</v>
-      </c>
-      <c r="I6" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="J6" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="K6" s="123" t="s">
-        <v>46</v>
-      </c>
-      <c r="L6" s="124" t="s">
+      <c r="F6" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="G6" s="25">
+        <v>10</v>
+      </c>
+      <c r="H6" s="25">
+        <v>30</v>
+      </c>
+      <c r="I6" s="25">
+        <v>20</v>
+      </c>
+      <c r="J6" s="25">
+        <v>40</v>
+      </c>
+      <c r="K6" s="97" t="s">
+        <v>138</v>
+      </c>
+      <c r="L6" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="M6" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="N6" s="24" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14">
-      <c r="B7" s="12">
+      <c r="M6" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="N6" s="20" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B7" s="9">
         <f>B6+1</f>
         <v>2</v>
       </c>
-      <c r="C7" s="110"/>
-      <c r="D7" s="31" t="s">
+      <c r="C7" s="108"/>
+      <c r="D7" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="G7" s="8">
+        <v>-100</v>
+      </c>
+      <c r="H7" s="50">
+        <v>10</v>
+      </c>
+      <c r="I7" s="50">
+        <v>5</v>
+      </c>
+      <c r="J7" s="50">
+        <v>15</v>
+      </c>
+      <c r="K7" s="95" t="s">
+        <v>138</v>
+      </c>
+      <c r="L7" s="96" t="s">
+        <v>139</v>
+      </c>
+      <c r="M7" s="50" t="s">
+        <v>150</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B8" s="9">
+        <v>3</v>
+      </c>
+      <c r="C8" s="108"/>
+      <c r="D8" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="G8" s="8">
+        <v>-100</v>
+      </c>
+      <c r="H8" s="50">
+        <v>10</v>
+      </c>
+      <c r="I8" s="50">
+        <v>5</v>
+      </c>
+      <c r="J8" s="50">
+        <v>15</v>
+      </c>
+      <c r="K8" s="95" t="s">
+        <v>138</v>
+      </c>
+      <c r="L8" s="96" t="s">
+        <v>140</v>
+      </c>
+      <c r="M8" s="50" t="s">
+        <v>150</v>
+      </c>
+      <c r="N8" s="20" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B9" s="9">
+        <v>4</v>
+      </c>
+      <c r="C9" s="108"/>
+      <c r="D9" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="G9" s="8">
+        <v>-100</v>
+      </c>
+      <c r="H9" s="50">
+        <v>10</v>
+      </c>
+      <c r="I9" s="50">
+        <v>5</v>
+      </c>
+      <c r="J9" s="50">
+        <v>15</v>
+      </c>
+      <c r="K9" s="95" t="s">
+        <v>138</v>
+      </c>
+      <c r="L9" s="96" t="s">
+        <v>141</v>
+      </c>
+      <c r="M9" s="50" t="s">
+        <v>150</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B10" s="20">
+        <v>5</v>
+      </c>
+      <c r="C10" s="108"/>
+      <c r="D10" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E10" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="H7" s="8">
-        <v>2010</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="K7" s="130" t="s">
-        <v>46</v>
-      </c>
-      <c r="L7" s="131"/>
-      <c r="M7" s="8" t="s">
+      <c r="F10" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="G10" s="8">
+        <v>10</v>
+      </c>
+      <c r="H10" s="50">
+        <v>10</v>
+      </c>
+      <c r="I10" s="50">
+        <v>20</v>
+      </c>
+      <c r="J10" s="50">
+        <v>300</v>
+      </c>
+      <c r="K10" s="95" t="s">
+        <v>152</v>
+      </c>
+      <c r="L10" s="96" t="s">
+        <v>140</v>
+      </c>
+      <c r="M10" s="50" t="s">
+        <v>150</v>
+      </c>
+      <c r="N10" s="20" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B11" s="9">
+        <v>6</v>
+      </c>
+      <c r="C11" s="108"/>
+      <c r="D11" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="G11" s="8">
+        <v>10</v>
+      </c>
+      <c r="H11" s="50">
+        <v>400</v>
+      </c>
+      <c r="I11" s="50">
+        <v>20</v>
+      </c>
+      <c r="J11" s="50">
+        <v>300</v>
+      </c>
+      <c r="K11" s="95" t="s">
+        <v>153</v>
+      </c>
+      <c r="L11" s="96" t="s">
+        <v>141</v>
+      </c>
+      <c r="M11" s="50" t="s">
+        <v>150</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B12" s="9">
+        <v>7</v>
+      </c>
+      <c r="C12" s="108"/>
+      <c r="D12" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="G12" s="8">
+        <v>100.5</v>
+      </c>
+      <c r="H12" s="50">
+        <v>10</v>
+      </c>
+      <c r="I12" s="50">
+        <v>5</v>
+      </c>
+      <c r="J12" s="50">
+        <v>15</v>
+      </c>
+      <c r="K12" s="95" t="s">
+        <v>138</v>
+      </c>
+      <c r="L12" s="96" t="s">
+        <v>142</v>
+      </c>
+      <c r="M12" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="N12" s="20" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B13" s="9">
+        <v>8</v>
+      </c>
+      <c r="C13" s="108"/>
+      <c r="D13" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="G13" s="8">
+        <v>10</v>
+      </c>
+      <c r="H13" s="50">
+        <v>5</v>
+      </c>
+      <c r="I13" s="50">
+        <v>5</v>
+      </c>
+      <c r="J13" s="50">
+        <v>15</v>
+      </c>
+      <c r="K13" s="95" t="s">
+        <v>138</v>
+      </c>
+      <c r="L13" s="96" t="s">
+        <v>143</v>
+      </c>
+      <c r="M13" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B14" s="20">
+        <v>9</v>
+      </c>
+      <c r="C14" s="108"/>
+      <c r="D14" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="G14" s="8">
+        <v>10</v>
+      </c>
+      <c r="H14" s="50">
+        <v>4</v>
+      </c>
+      <c r="I14" s="50">
+        <v>5</v>
+      </c>
+      <c r="J14" s="50">
+        <v>15</v>
+      </c>
+      <c r="K14" s="95" t="s">
+        <v>138</v>
+      </c>
+      <c r="L14" s="96" t="s">
+        <v>144</v>
+      </c>
+      <c r="M14" s="50" t="s">
+        <v>150</v>
+      </c>
+      <c r="N14" s="20" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B15" s="20">
+        <v>10</v>
+      </c>
+      <c r="C15" s="108"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="N7" s="12" t="s">
+      <c r="F15" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="H15" s="50">
+        <v>10</v>
+      </c>
+      <c r="I15" s="50">
+        <v>5</v>
+      </c>
+      <c r="J15" s="50">
+        <v>15</v>
+      </c>
+      <c r="K15" s="97" t="s">
+        <v>138</v>
+      </c>
+      <c r="L15" s="98" t="s">
+        <v>145</v>
+      </c>
+      <c r="M15" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="9">
+        <v>11</v>
+      </c>
+      <c r="C16" s="109"/>
+      <c r="D16" s="28" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="8" spans="2:14">
-      <c r="B8" s="12">
-        <f t="shared" ref="B8:B13" si="0">B7+1</f>
-        <v>3</v>
-      </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="31" t="s">
+      <c r="E16" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="N8" s="12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14">
-      <c r="B9" s="12">
-        <f t="shared" si="0"/>
+      <c r="F16" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="G16" s="8">
+        <v>-9.9999999999999995E-7</v>
+      </c>
+      <c r="H16" s="50">
+        <v>10</v>
+      </c>
+      <c r="I16" s="50">
+        <v>5</v>
+      </c>
+      <c r="J16" s="50">
+        <v>15</v>
+      </c>
+      <c r="K16" s="97" t="s">
+        <v>138</v>
+      </c>
+      <c r="L16" s="98" t="s">
+        <v>146</v>
+      </c>
+      <c r="M16" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="N16" s="20" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+    </row>
+    <row r="18" spans="2:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="C18" s="23"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="107"/>
+      <c r="L18" s="107"/>
+      <c r="M18" s="5"/>
+    </row>
+    <row r="19" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M19" s="5"/>
+    </row>
+    <row r="20" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="101" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20" s="103"/>
+      <c r="E20" s="103"/>
+      <c r="F20" s="104"/>
+      <c r="G20" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="H20" s="101" t="s">
+        <v>119</v>
+      </c>
+      <c r="I20" s="102"/>
+      <c r="J20" s="103"/>
+      <c r="K20" s="103"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="101" t="s">
+        <v>120</v>
+      </c>
+      <c r="N20" s="102"/>
+      <c r="O20" s="103"/>
+      <c r="P20" s="104"/>
+    </row>
+    <row r="21" spans="2:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="115" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" s="116" t="s">
+        <v>121</v>
+      </c>
+      <c r="D21" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="E21" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="F21" s="99" t="s">
+        <v>124</v>
+      </c>
+      <c r="G21" s="121" t="s">
+        <v>125</v>
+      </c>
+      <c r="H21" s="117" t="s">
+        <v>126</v>
+      </c>
+      <c r="I21" s="118"/>
+      <c r="J21" s="100" t="s">
+        <v>121</v>
+      </c>
+      <c r="K21" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="L21" s="99" t="s">
+        <v>123</v>
+      </c>
+      <c r="M21" s="105" t="s">
+        <v>126</v>
+      </c>
+      <c r="N21" s="100" t="s">
+        <v>121</v>
+      </c>
+      <c r="O21" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="P21" s="99" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B22" s="115"/>
+      <c r="C22" s="116"/>
+      <c r="D22" s="100"/>
+      <c r="E22" s="100"/>
+      <c r="F22" s="99"/>
+      <c r="G22" s="121"/>
+      <c r="H22" s="119"/>
+      <c r="I22" s="120"/>
+      <c r="J22" s="100"/>
+      <c r="K22" s="100"/>
+      <c r="L22" s="99"/>
+      <c r="M22" s="106"/>
+      <c r="N22" s="100"/>
+      <c r="O22" s="100"/>
+      <c r="P22" s="99"/>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B23" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="34">
+        <v>11</v>
+      </c>
+      <c r="D23" s="36">
         <v>4</v>
       </c>
-      <c r="C9" s="110"/>
-      <c r="D9" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="K9" s="132" t="s">
-        <v>50</v>
-      </c>
-      <c r="L9" s="133"/>
-      <c r="M9" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="N9" s="12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14">
-      <c r="B10" s="12">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="C10" s="110"/>
-      <c r="D10" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="H10" s="11">
-        <v>2010</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="K10" s="125" t="s">
-        <v>46</v>
-      </c>
-      <c r="L10" s="126"/>
-      <c r="M10" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="N10" s="12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14">
-      <c r="B11" s="12">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="C11" s="110"/>
-      <c r="D11" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="H11" s="11">
-        <v>2010</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="K11" s="125" t="s">
-        <v>46</v>
-      </c>
-      <c r="L11" s="126"/>
-      <c r="M11" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="N11" s="12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="2:14">
-      <c r="B12" s="12">
-        <f t="shared" si="0"/>
+      <c r="E23" s="36">
         <v>7</v>
       </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="H12" s="11">
-        <v>2010</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="K12" s="125" t="s">
-        <v>46</v>
-      </c>
-      <c r="L12" s="126"/>
-      <c r="M12" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="N12" s="12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="2:14" ht="15" thickBot="1">
-      <c r="B13" s="25">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="C13" s="111"/>
-      <c r="D13" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="G13" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="H13" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="I13" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="J13" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="K13" s="119" t="s">
-        <v>50</v>
-      </c>
-      <c r="L13" s="120"/>
-      <c r="M13" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="N13" s="25" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="2:14" ht="15" thickTop="1">
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="27"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="27"/>
-    </row>
-    <row r="15" spans="2:14" ht="14.45" customHeight="1">
-      <c r="B15" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="C15" s="27"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="109"/>
-      <c r="L15" s="109"/>
-      <c r="M15" s="7"/>
-    </row>
-    <row r="16" spans="2:14" ht="15" thickBot="1">
-      <c r="M16" s="7"/>
-    </row>
-    <row r="17" spans="2:16" ht="15" thickTop="1">
-      <c r="C17" s="98" t="s">
-        <v>120</v>
-      </c>
-      <c r="D17" s="100"/>
-      <c r="E17" s="100"/>
-      <c r="F17" s="101"/>
-      <c r="G17" s="39" t="s">
-        <v>121</v>
-      </c>
-      <c r="H17" s="98" t="s">
-        <v>122</v>
-      </c>
-      <c r="I17" s="99"/>
-      <c r="J17" s="100"/>
-      <c r="K17" s="100"/>
-      <c r="L17" s="101"/>
-      <c r="M17" s="98" t="s">
-        <v>123</v>
-      </c>
-      <c r="N17" s="99"/>
-      <c r="O17" s="100"/>
-      <c r="P17" s="101"/>
-    </row>
-    <row r="18" spans="2:16" ht="14.45" customHeight="1">
-      <c r="B18" s="117" t="s">
-        <v>106</v>
-      </c>
-      <c r="C18" s="118" t="s">
-        <v>124</v>
-      </c>
-      <c r="D18" s="96" t="s">
-        <v>125</v>
-      </c>
-      <c r="E18" s="96" t="s">
-        <v>126</v>
-      </c>
-      <c r="F18" s="97" t="s">
+      <c r="F23" s="37"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="113" t="s">
         <v>127</v>
       </c>
-      <c r="G18" s="108" t="s">
-        <v>128</v>
-      </c>
-      <c r="H18" s="104" t="s">
-        <v>129</v>
-      </c>
-      <c r="I18" s="105"/>
-      <c r="J18" s="96" t="s">
-        <v>124</v>
-      </c>
-      <c r="K18" s="96" t="s">
-        <v>125</v>
-      </c>
-      <c r="L18" s="97" t="s">
-        <v>126</v>
-      </c>
-      <c r="M18" s="102" t="s">
-        <v>129</v>
-      </c>
-      <c r="N18" s="96" t="s">
-        <v>124</v>
-      </c>
-      <c r="O18" s="96" t="s">
-        <v>125</v>
-      </c>
-      <c r="P18" s="97" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="19" spans="2:16">
-      <c r="B19" s="117"/>
-      <c r="C19" s="118"/>
-      <c r="D19" s="96"/>
-      <c r="E19" s="96"/>
-      <c r="F19" s="97"/>
-      <c r="G19" s="108"/>
-      <c r="H19" s="106"/>
-      <c r="I19" s="107"/>
-      <c r="J19" s="96"/>
-      <c r="K19" s="96"/>
-      <c r="L19" s="97"/>
-      <c r="M19" s="103"/>
-      <c r="N19" s="96"/>
-      <c r="O19" s="96"/>
-      <c r="P19" s="97"/>
-    </row>
-    <row r="20" spans="2:16">
-      <c r="B20" s="42" t="s">
-        <v>110</v>
-      </c>
-      <c r="C20" s="38">
-        <v>8</v>
-      </c>
-      <c r="D20" s="40">
-        <v>5</v>
-      </c>
-      <c r="E20" s="40">
-        <v>3</v>
-      </c>
-      <c r="F20" s="41"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="115" t="s">
-        <v>130</v>
-      </c>
-      <c r="I20" s="116"/>
-      <c r="J20" s="2">
-        <v>3</v>
-      </c>
-      <c r="K20" s="40">
-        <v>3</v>
-      </c>
-      <c r="L20" s="41">
+      <c r="I23" s="114"/>
+      <c r="J23" s="2">
         <v>0</v>
       </c>
-      <c r="M20" s="45" t="s">
-        <v>130</v>
-      </c>
-      <c r="N20" s="2">
-        <v>5</v>
-      </c>
-      <c r="O20" s="40">
-        <v>5</v>
-      </c>
-      <c r="P20" s="41">
+      <c r="K23" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="2:16">
-      <c r="M21" s="3"/>
+      <c r="L23" s="37">
+        <v>0</v>
+      </c>
+      <c r="M23" s="41" t="s">
+        <v>127</v>
+      </c>
+      <c r="N23" s="2">
+        <v>0</v>
+      </c>
+      <c r="O23" s="36">
+        <v>0</v>
+      </c>
+      <c r="P23" s="37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="M24" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="40">
     <mergeCell ref="B1:E1"/>
-    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="K16:L16"/>
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="K12:L12"/>
     <mergeCell ref="F4:L4"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="K7:L7"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="K8:L8"/>
     <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="B3:N3"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="C6:C13"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="H20:L20"/>
+    <mergeCell ref="H21:I22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="K21:K22"/>
+    <mergeCell ref="C6:C16"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="D4:D5"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="H17:L17"/>
-    <mergeCell ref="H18:I19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="O18:O19"/>
-    <mergeCell ref="P18:P19"/>
-    <mergeCell ref="M17:P17"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="N18:N19"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="O21:O22"/>
+    <mergeCell ref="P21:P22"/>
+    <mergeCell ref="M20:P20"/>
+    <mergeCell ref="M21:M22"/>
+    <mergeCell ref="N21:N22"/>
+    <mergeCell ref="K18:L18"/>
   </mergeCells>
+  <phoneticPr fontId="28" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -4346,13 +4514,36 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF0EB622-FDCF-4321-9FF5-C0B282D1670E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF0EB622-FDCF-4321-9FF5-C0B282D1670E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BC1EB47-4FFF-47F3-894F-DED91590EA19}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BC1EB47-4FFF-47F3-894F-DED91590EA19}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33EFF49E-866D-4BFD-B7FD-9BB436667B53}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33EFF49E-866D-4BFD-B7FD-9BB436667B53}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="fed1744a-f275-4023-9290-77fd546fd730"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Docs/Lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/Docs/Lab02/Lab02_BBT_TCs_Form.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0CEC025-83EE-44C9-BB65-F1879B49C42A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724B0AA4-A034-430C-B939-B65F45FF22CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,7 +13,7 @@
     <sheet name="F01.BVA" sheetId="3" r:id="rId3"/>
     <sheet name="BBT-TCs" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -117,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="162">
   <si>
     <t>VVSS, Info Romana, 2024-2025</t>
   </si>
@@ -751,6 +751,24 @@
   </si>
   <si>
     <t>DOUBLE_MAX</t>
+  </si>
+  <si>
+    <t>Functie testata:</t>
+  </si>
+  <si>
+    <t>public void addOutsourcePart(String name, double price, int inStock, int min, int  max, String partDynamicValue)</t>
+  </si>
+  <si>
+    <t>preconditii:</t>
+  </si>
+  <si>
+    <t>name, partDynamicValue - sir de caractere</t>
+  </si>
+  <si>
+    <t>inStock, min, max ∈ ℕ; min &lt;= inStock &lt;= max</t>
+  </si>
+  <si>
+    <t>price ∈ ℝ+</t>
   </si>
 </sst>
 </file>
@@ -1571,86 +1589,113 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1658,35 +1703,20 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1694,30 +1724,78 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1725,66 +1803,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2335,35 +2353,35 @@
       <c r="E1" s="54"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="74" t="s">
+      <c r="B3" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="76"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="61"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="G5" s="78" t="s">
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="G5" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
-      <c r="K5" s="78"/>
-      <c r="L5" s="78"/>
-      <c r="M5" s="78"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
+      <c r="L5" s="63"/>
+      <c r="M5" s="63"/>
+      <c r="N5" s="63"/>
+      <c r="O5" s="63"/>
+      <c r="P5" s="63"/>
+      <c r="Q5" s="63"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
@@ -2378,39 +2396,39 @@
       <c r="E6" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="79" t="s">
+      <c r="G6" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="63" t="s">
+      <c r="H6" s="78" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="61" t="s">
+      <c r="I6" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="66"/>
-      <c r="K6" s="66"/>
-      <c r="L6" s="66"/>
-      <c r="M6" s="66"/>
-      <c r="N6" s="66"/>
-      <c r="O6" s="62"/>
-      <c r="P6" s="65" t="s">
+      <c r="J6" s="81"/>
+      <c r="K6" s="81"/>
+      <c r="L6" s="81"/>
+      <c r="M6" s="81"/>
+      <c r="N6" s="81"/>
+      <c r="O6" s="77"/>
+      <c r="P6" s="80" t="s">
         <v>31</v>
       </c>
-      <c r="Q6" s="65"/>
+      <c r="Q6" s="80"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="71" t="s">
+      <c r="C7" s="56" t="s">
         <v>32</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="64"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="79"/>
       <c r="I7" s="19" t="s">
         <v>33</v>
       </c>
@@ -2426,20 +2444,20 @@
       <c r="M7" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="N7" s="61" t="s">
+      <c r="N7" s="76" t="s">
         <v>38</v>
       </c>
-      <c r="O7" s="62"/>
-      <c r="P7" s="61" t="s">
+      <c r="O7" s="77"/>
+      <c r="P7" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="Q7" s="62"/>
+      <c r="Q7" s="77"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="71"/>
+      <c r="C8" s="56"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
         <v>40</v>
@@ -2465,22 +2483,22 @@
       <c r="M8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N8" s="57" t="s">
+      <c r="N8" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="O8" s="58" t="s">
+      <c r="O8" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="P8" s="57" t="s">
+      <c r="P8" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="Q8" s="58"/>
+      <c r="Q8" s="75"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="71" t="s">
+      <c r="C9" s="56" t="s">
         <v>49</v>
       </c>
       <c r="D9" s="4" t="s">
@@ -2508,22 +2526,22 @@
       <c r="M9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N9" s="57" t="s">
+      <c r="N9" s="74" t="s">
         <v>50</v>
       </c>
-      <c r="O9" s="58" t="s">
+      <c r="O9" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="P9" s="57" t="s">
+      <c r="P9" s="74" t="s">
         <v>50</v>
       </c>
-      <c r="Q9" s="58"/>
+      <c r="Q9" s="75"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="71"/>
+      <c r="C10" s="56"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
         <v>53</v>
@@ -2549,20 +2567,20 @@
       <c r="M10" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="N10" s="69" t="s">
+      <c r="N10" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="O10" s="70"/>
-      <c r="P10" s="69" t="s">
+      <c r="O10" s="69"/>
+      <c r="P10" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="Q10" s="70"/>
+      <c r="Q10" s="69"/>
     </row>
     <row r="11" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="71" t="s">
+      <c r="C11" s="56" t="s">
         <v>57</v>
       </c>
       <c r="D11" s="4" t="s">
@@ -2590,20 +2608,20 @@
       <c r="M11" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N11" s="69" t="s">
+      <c r="N11" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="O11" s="70"/>
-      <c r="P11" s="69" t="s">
+      <c r="O11" s="69"/>
+      <c r="P11" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="Q11" s="70"/>
+      <c r="Q11" s="69"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>6</v>
       </c>
-      <c r="C12" s="71"/>
+      <c r="C12" s="56"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
         <v>59</v>
@@ -2633,16 +2651,16 @@
         <v>46</v>
       </c>
       <c r="O12" s="6"/>
-      <c r="P12" s="67" t="s">
+      <c r="P12" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="Q12" s="68"/>
+      <c r="Q12" s="71"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="72" t="s">
+      <c r="C13" s="57" t="s">
         <v>63</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -2670,20 +2688,20 @@
       <c r="M13" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="N13" s="67" t="s">
+      <c r="N13" s="70" t="s">
         <v>50</v>
       </c>
-      <c r="O13" s="68"/>
-      <c r="P13" s="67" t="s">
+      <c r="O13" s="71"/>
+      <c r="P13" s="70" t="s">
         <v>50</v>
       </c>
-      <c r="Q13" s="68"/>
+      <c r="Q13" s="71"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="4">
         <v>8</v>
       </c>
-      <c r="C14" s="73"/>
+      <c r="C14" s="58"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
         <v>64</v>
@@ -2709,18 +2727,18 @@
       <c r="M14" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="N14" s="81" t="s">
+      <c r="N14" s="66" t="s">
         <v>65</v>
       </c>
-      <c r="O14" s="82"/>
-      <c r="P14" s="59"/>
-      <c r="Q14" s="60"/>
+      <c r="O14" s="67"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="73"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="71" t="s">
+      <c r="C15" s="56" t="s">
         <v>50</v>
       </c>
       <c r="D15" s="4"/>
@@ -2736,16 +2754,16 @@
       <c r="K15" s="14"/>
       <c r="L15" s="14"/>
       <c r="M15" s="14"/>
-      <c r="N15" s="57"/>
-      <c r="O15" s="58"/>
-      <c r="P15" s="59"/>
-      <c r="Q15" s="60"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="75"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="73"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B16" s="4">
         <v>10</v>
       </c>
-      <c r="C16" s="71"/>
+      <c r="C16" s="56"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="G16" s="15"/>
@@ -2755,16 +2773,16 @@
       <c r="K16" s="14"/>
       <c r="L16" s="14"/>
       <c r="M16" s="14"/>
-      <c r="N16" s="57"/>
-      <c r="O16" s="58"/>
-      <c r="P16" s="59"/>
-      <c r="Q16" s="60"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="75"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="73"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" s="4">
         <v>11</v>
       </c>
-      <c r="C17" s="71" t="s">
+      <c r="C17" s="56" t="s">
         <v>50</v>
       </c>
       <c r="D17" s="4"/>
@@ -2776,16 +2794,16 @@
       <c r="K17" s="14"/>
       <c r="L17" s="14"/>
       <c r="M17" s="14"/>
-      <c r="N17" s="57"/>
-      <c r="O17" s="58"/>
-      <c r="P17" s="59"/>
-      <c r="Q17" s="60"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="75"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="73"/>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18" s="4">
         <v>12</v>
       </c>
-      <c r="C18" s="71"/>
+      <c r="C18" s="56"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="G18" s="15"/>
@@ -2795,16 +2813,16 @@
       <c r="K18" s="14"/>
       <c r="L18" s="14"/>
       <c r="M18" s="14"/>
-      <c r="N18" s="57"/>
-      <c r="O18" s="58"/>
-      <c r="P18" s="59"/>
-      <c r="Q18" s="60"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="75"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="73"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="4">
         <v>13</v>
       </c>
-      <c r="C19" s="71" t="s">
+      <c r="C19" s="56" t="s">
         <v>50</v>
       </c>
       <c r="D19" s="4"/>
@@ -2816,16 +2834,16 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="58"/>
-      <c r="P19" s="59"/>
-      <c r="Q19" s="60"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="75"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="73"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
         <v>14</v>
       </c>
-      <c r="C20" s="71"/>
+      <c r="C20" s="56"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
@@ -2833,11 +2851,36 @@
       <c r="D22" t="s">
         <v>66</v>
       </c>
-      <c r="F22" s="56"/>
-      <c r="G22" s="56"/>
+      <c r="F22" s="82"/>
+      <c r="G22" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="41">
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="I6:O6"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="N11:O11"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="C7:C8"/>
@@ -2854,31 +2897,6 @@
     <mergeCell ref="P10:Q10"/>
     <mergeCell ref="P11:Q11"/>
     <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="I6:O6"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="P15:Q15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2919,14 +2937,14 @@
       <c r="E1" s="54"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B3" s="74" t="s">
+      <c r="B3" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="76"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="61"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="89" t="s">
@@ -2935,20 +2953,20 @@
       <c r="C5" s="89"/>
       <c r="D5" s="89"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="78" t="s">
+      <c r="G5" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
-      <c r="K5" s="78"/>
-      <c r="L5" s="78"/>
-      <c r="M5" s="78"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
+      <c r="L5" s="63"/>
+      <c r="M5" s="63"/>
+      <c r="N5" s="63"/>
+      <c r="O5" s="63"/>
+      <c r="P5" s="63"/>
+      <c r="Q5" s="63"/>
+      <c r="R5" s="63"/>
     </row>
     <row r="6" spans="2:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
@@ -2961,45 +2979,45 @@
         <v>67</v>
       </c>
       <c r="E6" s="7"/>
-      <c r="G6" s="79" t="s">
+      <c r="G6" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="79" t="s">
+      <c r="H6" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="I6" s="79" t="s">
+      <c r="I6" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="J6" s="63" t="s">
+      <c r="J6" s="78" t="s">
         <v>73</v>
       </c>
-      <c r="K6" s="85" t="s">
+      <c r="K6" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="L6" s="86"/>
-      <c r="M6" s="86"/>
-      <c r="N6" s="86"/>
-      <c r="O6" s="86"/>
-      <c r="P6" s="87"/>
-      <c r="Q6" s="85" t="s">
+      <c r="L6" s="94"/>
+      <c r="M6" s="94"/>
+      <c r="N6" s="94"/>
+      <c r="O6" s="94"/>
+      <c r="P6" s="91"/>
+      <c r="Q6" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="R6" s="87"/>
+      <c r="R6" s="91"/>
     </row>
     <row r="7" spans="2:18" ht="45" x14ac:dyDescent="0.25">
-      <c r="B7" s="72">
+      <c r="B7" s="57">
         <v>1</v>
       </c>
-      <c r="C7" s="91" t="s">
+      <c r="C7" s="84" t="s">
         <v>74</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="80"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="64"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
+      <c r="I7" s="65"/>
+      <c r="J7" s="79"/>
       <c r="K7" s="19" t="s">
         <v>33</v>
       </c>
@@ -3018,14 +3036,14 @@
       <c r="P7" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="Q7" s="61" t="s">
+      <c r="Q7" s="76" t="s">
         <v>76</v>
       </c>
-      <c r="R7" s="62"/>
+      <c r="R7" s="77"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B8" s="90"/>
-      <c r="C8" s="92"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="85"/>
       <c r="D8" s="2" t="s">
         <v>77</v>
       </c>
@@ -3045,12 +3063,12 @@
       <c r="N8" s="30"/>
       <c r="O8" s="30"/>
       <c r="P8" s="30"/>
-      <c r="Q8" s="83"/>
-      <c r="R8" s="84"/>
+      <c r="Q8" s="92"/>
+      <c r="R8" s="93"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B9" s="90"/>
-      <c r="C9" s="92"/>
+      <c r="B9" s="83"/>
+      <c r="C9" s="85"/>
       <c r="D9" s="2" t="s">
         <v>79</v>
       </c>
@@ -3080,14 +3098,14 @@
       <c r="P9" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="Q9" s="67" t="s">
+      <c r="Q9" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="R9" s="68"/>
+      <c r="R9" s="71"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B10" s="90"/>
-      <c r="C10" s="92"/>
+      <c r="B10" s="83"/>
+      <c r="C10" s="85"/>
       <c r="D10" s="2" t="s">
         <v>81</v>
       </c>
@@ -3117,14 +3135,14 @@
       <c r="P10" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="Q10" s="83" t="s">
+      <c r="Q10" s="92" t="s">
         <v>48</v>
       </c>
-      <c r="R10" s="84"/>
+      <c r="R10" s="93"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B11" s="90"/>
-      <c r="C11" s="92"/>
+      <c r="B11" s="83"/>
+      <c r="C11" s="85"/>
       <c r="D11" s="2" t="s">
         <v>85</v>
       </c>
@@ -3154,14 +3172,14 @@
       <c r="P11" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="Q11" s="83" t="s">
+      <c r="Q11" s="92" t="s">
         <v>48</v>
       </c>
-      <c r="R11" s="84"/>
+      <c r="R11" s="93"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B12" s="73"/>
-      <c r="C12" s="93"/>
+      <c r="B12" s="58"/>
+      <c r="C12" s="86"/>
       <c r="D12" s="2" t="s">
         <v>87</v>
       </c>
@@ -3191,16 +3209,16 @@
       <c r="P12" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="Q12" s="83" t="s">
+      <c r="Q12" s="92" t="s">
         <v>48</v>
       </c>
-      <c r="R12" s="84"/>
+      <c r="R12" s="93"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B13" s="72">
+      <c r="B13" s="57">
         <v>2</v>
       </c>
-      <c r="C13" s="72" t="s">
+      <c r="C13" s="57" t="s">
         <v>89</v>
       </c>
       <c r="D13" s="2" t="s">
@@ -3234,14 +3252,14 @@
       <c r="P13" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="Q13" s="67" t="s">
+      <c r="Q13" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="R13" s="68"/>
+      <c r="R13" s="71"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B14" s="90"/>
-      <c r="C14" s="90"/>
+      <c r="B14" s="83"/>
+      <c r="C14" s="83"/>
       <c r="D14" s="2" t="s">
         <v>92</v>
       </c>
@@ -3263,12 +3281,12 @@
       <c r="N14" s="30"/>
       <c r="O14" s="30"/>
       <c r="P14" s="30"/>
-      <c r="Q14" s="83"/>
-      <c r="R14" s="84"/>
+      <c r="Q14" s="92"/>
+      <c r="R14" s="93"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B15" s="90"/>
-      <c r="C15" s="90"/>
+      <c r="B15" s="83"/>
+      <c r="C15" s="83"/>
       <c r="D15" s="2" t="s">
         <v>93</v>
       </c>
@@ -3290,12 +3308,12 @@
       <c r="N15" s="30"/>
       <c r="O15" s="30"/>
       <c r="P15" s="30"/>
-      <c r="Q15" s="83"/>
-      <c r="R15" s="84"/>
+      <c r="Q15" s="92"/>
+      <c r="R15" s="93"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B16" s="90"/>
-      <c r="C16" s="90"/>
+      <c r="B16" s="83"/>
+      <c r="C16" s="83"/>
       <c r="D16" s="2" t="s">
         <v>94</v>
       </c>
@@ -3311,12 +3329,12 @@
       <c r="N16" s="30"/>
       <c r="O16" s="30"/>
       <c r="P16" s="30"/>
-      <c r="Q16" s="83"/>
-      <c r="R16" s="84"/>
+      <c r="Q16" s="92"/>
+      <c r="R16" s="93"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B17" s="90"/>
-      <c r="C17" s="90"/>
+      <c r="B17" s="83"/>
+      <c r="C17" s="83"/>
       <c r="D17" s="2" t="s">
         <v>95</v>
       </c>
@@ -3332,12 +3350,12 @@
       <c r="N17" s="30"/>
       <c r="O17" s="30"/>
       <c r="P17" s="30"/>
-      <c r="Q17" s="83"/>
-      <c r="R17" s="84"/>
+      <c r="Q17" s="92"/>
+      <c r="R17" s="93"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B18" s="73"/>
-      <c r="C18" s="73"/>
+      <c r="B18" s="58"/>
+      <c r="C18" s="58"/>
       <c r="D18" s="2" t="s">
         <v>96</v>
       </c>
@@ -3353,14 +3371,14 @@
       <c r="N18" s="30"/>
       <c r="O18" s="30"/>
       <c r="P18" s="30"/>
-      <c r="Q18" s="83"/>
-      <c r="R18" s="84"/>
+      <c r="Q18" s="92"/>
+      <c r="R18" s="93"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B19" s="72">
+      <c r="B19" s="57">
         <v>3</v>
       </c>
-      <c r="C19" s="91" t="s">
+      <c r="C19" s="84" t="s">
         <v>97</v>
       </c>
       <c r="D19" s="2" t="s">
@@ -3378,12 +3396,12 @@
       <c r="N19" s="30"/>
       <c r="O19" s="30"/>
       <c r="P19" s="30"/>
-      <c r="Q19" s="83"/>
-      <c r="R19" s="84"/>
+      <c r="Q19" s="92"/>
+      <c r="R19" s="93"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B20" s="90"/>
-      <c r="C20" s="92"/>
+      <c r="B20" s="83"/>
+      <c r="C20" s="85"/>
       <c r="D20" s="2" t="s">
         <v>99</v>
       </c>
@@ -3399,12 +3417,12 @@
       <c r="N20" s="30"/>
       <c r="O20" s="30"/>
       <c r="P20" s="30"/>
-      <c r="Q20" s="83"/>
-      <c r="R20" s="84"/>
+      <c r="Q20" s="92"/>
+      <c r="R20" s="93"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B21" s="90"/>
-      <c r="C21" s="92"/>
+      <c r="B21" s="83"/>
+      <c r="C21" s="85"/>
       <c r="D21" s="2" t="s">
         <v>100</v>
       </c>
@@ -3420,12 +3438,12 @@
       <c r="N21" s="30"/>
       <c r="O21" s="30"/>
       <c r="P21" s="30"/>
-      <c r="Q21" s="83"/>
-      <c r="R21" s="84"/>
+      <c r="Q21" s="92"/>
+      <c r="R21" s="93"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B22" s="90"/>
-      <c r="C22" s="92"/>
+      <c r="B22" s="83"/>
+      <c r="C22" s="85"/>
       <c r="D22" s="2" t="s">
         <v>101</v>
       </c>
@@ -3441,12 +3459,12 @@
       <c r="N22" s="30"/>
       <c r="O22" s="30"/>
       <c r="P22" s="30"/>
-      <c r="Q22" s="83"/>
-      <c r="R22" s="84"/>
+      <c r="Q22" s="92"/>
+      <c r="R22" s="93"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B23" s="90"/>
-      <c r="C23" s="92"/>
+      <c r="B23" s="83"/>
+      <c r="C23" s="85"/>
       <c r="D23" s="2" t="s">
         <v>102</v>
       </c>
@@ -3462,12 +3480,12 @@
       <c r="N23" s="30"/>
       <c r="O23" s="30"/>
       <c r="P23" s="30"/>
-      <c r="Q23" s="83"/>
-      <c r="R23" s="84"/>
+      <c r="Q23" s="92"/>
+      <c r="R23" s="93"/>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B24" s="73"/>
-      <c r="C24" s="93"/>
+      <c r="B24" s="58"/>
+      <c r="C24" s="86"/>
       <c r="D24" s="2" t="s">
         <v>103</v>
       </c>
@@ -3483,14 +3501,14 @@
       <c r="N24" s="30"/>
       <c r="O24" s="30"/>
       <c r="P24" s="30"/>
-      <c r="Q24" s="83"/>
-      <c r="R24" s="84"/>
+      <c r="Q24" s="92"/>
+      <c r="R24" s="93"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B25" s="72">
+      <c r="B25" s="57">
         <v>4</v>
       </c>
-      <c r="C25" s="91" t="s">
+      <c r="C25" s="84" t="s">
         <v>50</v>
       </c>
       <c r="D25" s="2" t="s">
@@ -3508,31 +3526,31 @@
       <c r="N25" s="30"/>
       <c r="O25" s="30"/>
       <c r="P25" s="30"/>
-      <c r="Q25" s="83"/>
-      <c r="R25" s="84"/>
+      <c r="Q25" s="92"/>
+      <c r="R25" s="93"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B26" s="90"/>
-      <c r="C26" s="92"/>
+      <c r="B26" s="83"/>
+      <c r="C26" s="85"/>
       <c r="D26" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B27" s="90"/>
-      <c r="C27" s="92"/>
+      <c r="B27" s="83"/>
+      <c r="C27" s="85"/>
       <c r="D27" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B28" s="90"/>
-      <c r="C28" s="92"/>
+      <c r="B28" s="83"/>
+      <c r="C28" s="85"/>
       <c r="D28" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
+      <c r="G28" s="82"/>
+      <c r="H28" s="82"/>
       <c r="I28" s="88"/>
       <c r="J28" s="88"/>
       <c r="K28" s="88"/>
@@ -3541,27 +3559,51 @@
       <c r="N28" s="39"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B29" s="90"/>
-      <c r="C29" s="92"/>
+      <c r="B29" s="83"/>
+      <c r="C29" s="85"/>
       <c r="D29" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I29" s="94"/>
-      <c r="J29" s="94"/>
-      <c r="K29" s="94"/>
-      <c r="L29" s="94"/>
-      <c r="M29" s="94"/>
+      <c r="I29" s="87"/>
+      <c r="J29" s="87"/>
+      <c r="K29" s="87"/>
+      <c r="L29" s="87"/>
+      <c r="M29" s="87"/>
       <c r="N29" s="40"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B30" s="73"/>
-      <c r="C30" s="93"/>
+      <c r="B30" s="58"/>
+      <c r="C30" s="86"/>
       <c r="D30" s="2" t="s">
         <v>50</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="K6:P6"/>
+    <mergeCell ref="Q10:R10"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I28:M28"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="Q9:R9"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="I6:I7"/>
@@ -3578,30 +3620,6 @@
     <mergeCell ref="G5:R5"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="I28:M28"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="K6:P6"/>
-    <mergeCell ref="Q10:R10"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="Q12:R12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3614,7 +3632,7 @@
   <sheetPr>
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="B1:P24"/>
+  <dimension ref="B1:P31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="14.5703125" customWidth="1"/>
@@ -3636,54 +3654,54 @@
       <c r="E1" s="54"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="127" t="s">
+      <c r="B3" s="104" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="127"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="127"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="127"/>
-      <c r="J3" s="127"/>
-      <c r="K3" s="127"/>
-      <c r="L3" s="127"/>
-      <c r="M3" s="127"/>
-      <c r="N3" s="127"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="104"/>
+      <c r="I3" s="104"/>
+      <c r="J3" s="104"/>
+      <c r="K3" s="104"/>
+      <c r="L3" s="104"/>
+      <c r="M3" s="104"/>
+      <c r="N3" s="104"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" s="79" t="s">
+      <c r="B4" s="64" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="125" t="s">
+      <c r="C4" s="102" t="s">
         <v>106</v>
       </c>
-      <c r="D4" s="111" t="s">
+      <c r="D4" s="118" t="s">
         <v>107</v>
       </c>
-      <c r="E4" s="63" t="s">
+      <c r="E4" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="F4" s="61" t="s">
+      <c r="F4" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="66"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
-      <c r="K4" s="66"/>
-      <c r="L4" s="62"/>
-      <c r="M4" s="65" t="s">
+      <c r="G4" s="81"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="81"/>
+      <c r="L4" s="77"/>
+      <c r="M4" s="80" t="s">
         <v>31</v>
       </c>
-      <c r="N4" s="65"/>
+      <c r="N4" s="80"/>
     </row>
     <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="110"/>
-      <c r="C5" s="126"/>
-      <c r="D5" s="112"/>
-      <c r="E5" s="124"/>
+      <c r="B5" s="117"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="101"/>
       <c r="F5" s="22" t="s">
         <v>128</v>
       </c>
@@ -3699,10 +3717,10 @@
       <c r="J5" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="K5" s="122" t="s">
+      <c r="K5" s="97" t="s">
         <v>133</v>
       </c>
-      <c r="L5" s="123"/>
+      <c r="L5" s="98"/>
       <c r="M5" s="22" t="s">
         <v>39</v>
       </c>
@@ -3714,7 +3732,7 @@
       <c r="B6" s="20">
         <v>1</v>
       </c>
-      <c r="C6" s="108" t="s">
+      <c r="C6" s="115" t="s">
         <v>110</v>
       </c>
       <c r="D6" s="26" t="s">
@@ -3738,10 +3756,10 @@
       <c r="J6" s="25">
         <v>40</v>
       </c>
-      <c r="K6" s="97" t="s">
+      <c r="K6" s="95" t="s">
         <v>138</v>
       </c>
-      <c r="L6" s="98" t="s">
+      <c r="L6" s="96" t="s">
         <v>47</v>
       </c>
       <c r="M6" s="25" t="s">
@@ -3756,7 +3774,7 @@
         <f>B6+1</f>
         <v>2</v>
       </c>
-      <c r="C7" s="108"/>
+      <c r="C7" s="115"/>
       <c r="D7" s="27" t="s">
         <v>134</v>
       </c>
@@ -3778,10 +3796,10 @@
       <c r="J7" s="50">
         <v>15</v>
       </c>
-      <c r="K7" s="95" t="s">
+      <c r="K7" s="99" t="s">
         <v>138</v>
       </c>
-      <c r="L7" s="96" t="s">
+      <c r="L7" s="100" t="s">
         <v>139</v>
       </c>
       <c r="M7" s="50" t="s">
@@ -3795,7 +3813,7 @@
       <c r="B8" s="9">
         <v>3</v>
       </c>
-      <c r="C8" s="108"/>
+      <c r="C8" s="115"/>
       <c r="D8" s="27" t="s">
         <v>112</v>
       </c>
@@ -3817,10 +3835,10 @@
       <c r="J8" s="50">
         <v>15</v>
       </c>
-      <c r="K8" s="95" t="s">
+      <c r="K8" s="99" t="s">
         <v>138</v>
       </c>
-      <c r="L8" s="96" t="s">
+      <c r="L8" s="100" t="s">
         <v>140</v>
       </c>
       <c r="M8" s="50" t="s">
@@ -3834,7 +3852,7 @@
       <c r="B9" s="9">
         <v>4</v>
       </c>
-      <c r="C9" s="108"/>
+      <c r="C9" s="115"/>
       <c r="D9" s="27" t="s">
         <v>135</v>
       </c>
@@ -3856,10 +3874,10 @@
       <c r="J9" s="50">
         <v>15</v>
       </c>
-      <c r="K9" s="95" t="s">
+      <c r="K9" s="99" t="s">
         <v>138</v>
       </c>
-      <c r="L9" s="96" t="s">
+      <c r="L9" s="100" t="s">
         <v>141</v>
       </c>
       <c r="M9" s="50" t="s">
@@ -3873,7 +3891,7 @@
       <c r="B10" s="20">
         <v>5</v>
       </c>
-      <c r="C10" s="108"/>
+      <c r="C10" s="115"/>
       <c r="D10" s="27" t="s">
         <v>113</v>
       </c>
@@ -3895,10 +3913,10 @@
       <c r="J10" s="50">
         <v>300</v>
       </c>
-      <c r="K10" s="95" t="s">
+      <c r="K10" s="99" t="s">
         <v>152</v>
       </c>
-      <c r="L10" s="96" t="s">
+      <c r="L10" s="100" t="s">
         <v>140</v>
       </c>
       <c r="M10" s="50" t="s">
@@ -3912,7 +3930,7 @@
       <c r="B11" s="9">
         <v>6</v>
       </c>
-      <c r="C11" s="108"/>
+      <c r="C11" s="115"/>
       <c r="D11" s="27" t="s">
         <v>136</v>
       </c>
@@ -3934,10 +3952,10 @@
       <c r="J11" s="50">
         <v>300</v>
       </c>
-      <c r="K11" s="95" t="s">
+      <c r="K11" s="99" t="s">
         <v>153</v>
       </c>
-      <c r="L11" s="96" t="s">
+      <c r="L11" s="100" t="s">
         <v>141</v>
       </c>
       <c r="M11" s="50" t="s">
@@ -3951,7 +3969,7 @@
       <c r="B12" s="9">
         <v>7</v>
       </c>
-      <c r="C12" s="108"/>
+      <c r="C12" s="115"/>
       <c r="D12" s="27" t="s">
         <v>154</v>
       </c>
@@ -3973,10 +3991,10 @@
       <c r="J12" s="50">
         <v>15</v>
       </c>
-      <c r="K12" s="95" t="s">
+      <c r="K12" s="99" t="s">
         <v>138</v>
       </c>
-      <c r="L12" s="96" t="s">
+      <c r="L12" s="100" t="s">
         <v>142</v>
       </c>
       <c r="M12" s="50" t="s">
@@ -3990,7 +4008,7 @@
       <c r="B13" s="9">
         <v>8</v>
       </c>
-      <c r="C13" s="108"/>
+      <c r="C13" s="115"/>
       <c r="D13" s="27" t="s">
         <v>52</v>
       </c>
@@ -4012,10 +4030,10 @@
       <c r="J13" s="50">
         <v>15</v>
       </c>
-      <c r="K13" s="95" t="s">
+      <c r="K13" s="99" t="s">
         <v>138</v>
       </c>
-      <c r="L13" s="96" t="s">
+      <c r="L13" s="100" t="s">
         <v>143</v>
       </c>
       <c r="M13" s="50" t="s">
@@ -4029,7 +4047,7 @@
       <c r="B14" s="20">
         <v>9</v>
       </c>
-      <c r="C14" s="108"/>
+      <c r="C14" s="115"/>
       <c r="D14" s="27" t="s">
         <v>52</v>
       </c>
@@ -4051,10 +4069,10 @@
       <c r="J14" s="50">
         <v>15</v>
       </c>
-      <c r="K14" s="95" t="s">
+      <c r="K14" s="99" t="s">
         <v>138</v>
       </c>
-      <c r="L14" s="96" t="s">
+      <c r="L14" s="100" t="s">
         <v>144</v>
       </c>
       <c r="M14" s="50" t="s">
@@ -4068,7 +4086,7 @@
       <c r="B15" s="20">
         <v>10</v>
       </c>
-      <c r="C15" s="108"/>
+      <c r="C15" s="115"/>
       <c r="D15" s="48"/>
       <c r="E15" s="9" t="s">
         <v>114</v>
@@ -4088,10 +4106,10 @@
       <c r="J15" s="50">
         <v>15</v>
       </c>
-      <c r="K15" s="97" t="s">
+      <c r="K15" s="95" t="s">
         <v>138</v>
       </c>
-      <c r="L15" s="98" t="s">
+      <c r="L15" s="96" t="s">
         <v>145</v>
       </c>
       <c r="M15" s="49" t="s">
@@ -4105,7 +4123,7 @@
       <c r="B16" s="9">
         <v>11</v>
       </c>
-      <c r="C16" s="109"/>
+      <c r="C16" s="116"/>
       <c r="D16" s="28" t="s">
         <v>50</v>
       </c>
@@ -4127,10 +4145,10 @@
       <c r="J16" s="50">
         <v>15</v>
       </c>
-      <c r="K16" s="97" t="s">
+      <c r="K16" s="95" t="s">
         <v>138</v>
       </c>
-      <c r="L16" s="98" t="s">
+      <c r="L16" s="96" t="s">
         <v>146</v>
       </c>
       <c r="M16" s="21" t="s">
@@ -4167,98 +4185,98 @@
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
-      <c r="K18" s="107"/>
-      <c r="L18" s="107"/>
+      <c r="K18" s="127"/>
+      <c r="L18" s="127"/>
       <c r="M18" s="5"/>
     </row>
     <row r="19" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M19" s="5"/>
     </row>
     <row r="20" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C20" s="101" t="s">
+      <c r="C20" s="106" t="s">
         <v>117</v>
       </c>
-      <c r="D20" s="103"/>
-      <c r="E20" s="103"/>
-      <c r="F20" s="104"/>
+      <c r="D20" s="107"/>
+      <c r="E20" s="107"/>
+      <c r="F20" s="108"/>
       <c r="G20" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="H20" s="101" t="s">
+      <c r="H20" s="106" t="s">
         <v>119</v>
       </c>
-      <c r="I20" s="102"/>
-      <c r="J20" s="103"/>
-      <c r="K20" s="103"/>
-      <c r="L20" s="104"/>
-      <c r="M20" s="101" t="s">
+      <c r="I20" s="109"/>
+      <c r="J20" s="107"/>
+      <c r="K20" s="107"/>
+      <c r="L20" s="108"/>
+      <c r="M20" s="106" t="s">
         <v>120</v>
       </c>
-      <c r="N20" s="102"/>
-      <c r="O20" s="103"/>
-      <c r="P20" s="104"/>
+      <c r="N20" s="109"/>
+      <c r="O20" s="107"/>
+      <c r="P20" s="108"/>
     </row>
     <row r="21" spans="2:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="115" t="s">
+      <c r="B21" s="122" t="s">
         <v>106</v>
       </c>
-      <c r="C21" s="116" t="s">
+      <c r="C21" s="123" t="s">
         <v>121</v>
       </c>
-      <c r="D21" s="100" t="s">
+      <c r="D21" s="105" t="s">
         <v>122</v>
       </c>
-      <c r="E21" s="100" t="s">
+      <c r="E21" s="105" t="s">
         <v>123</v>
       </c>
-      <c r="F21" s="99" t="s">
+      <c r="F21" s="124" t="s">
         <v>124</v>
       </c>
-      <c r="G21" s="121" t="s">
+      <c r="G21" s="114" t="s">
         <v>125</v>
       </c>
-      <c r="H21" s="117" t="s">
+      <c r="H21" s="110" t="s">
         <v>126</v>
       </c>
-      <c r="I21" s="118"/>
-      <c r="J21" s="100" t="s">
+      <c r="I21" s="111"/>
+      <c r="J21" s="105" t="s">
         <v>121</v>
       </c>
-      <c r="K21" s="100" t="s">
+      <c r="K21" s="105" t="s">
         <v>122</v>
       </c>
-      <c r="L21" s="99" t="s">
+      <c r="L21" s="124" t="s">
         <v>123</v>
       </c>
-      <c r="M21" s="105" t="s">
+      <c r="M21" s="125" t="s">
         <v>126</v>
       </c>
-      <c r="N21" s="100" t="s">
+      <c r="N21" s="105" t="s">
         <v>121</v>
       </c>
-      <c r="O21" s="100" t="s">
+      <c r="O21" s="105" t="s">
         <v>122</v>
       </c>
-      <c r="P21" s="99" t="s">
+      <c r="P21" s="124" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B22" s="115"/>
-      <c r="C22" s="116"/>
-      <c r="D22" s="100"/>
-      <c r="E22" s="100"/>
-      <c r="F22" s="99"/>
-      <c r="G22" s="121"/>
-      <c r="H22" s="119"/>
-      <c r="I22" s="120"/>
-      <c r="J22" s="100"/>
-      <c r="K22" s="100"/>
-      <c r="L22" s="99"/>
-      <c r="M22" s="106"/>
-      <c r="N22" s="100"/>
-      <c r="O22" s="100"/>
-      <c r="P22" s="99"/>
+      <c r="B22" s="122"/>
+      <c r="C22" s="123"/>
+      <c r="D22" s="105"/>
+      <c r="E22" s="105"/>
+      <c r="F22" s="124"/>
+      <c r="G22" s="114"/>
+      <c r="H22" s="112"/>
+      <c r="I22" s="113"/>
+      <c r="J22" s="105"/>
+      <c r="K22" s="105"/>
+      <c r="L22" s="124"/>
+      <c r="M22" s="126"/>
+      <c r="N22" s="105"/>
+      <c r="O22" s="105"/>
+      <c r="P22" s="124"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B23" s="38" t="s">
@@ -4275,10 +4293,10 @@
       </c>
       <c r="F23" s="37"/>
       <c r="G23" s="42"/>
-      <c r="H23" s="113" t="s">
+      <c r="H23" s="120" t="s">
         <v>127</v>
       </c>
-      <c r="I23" s="114"/>
+      <c r="I23" s="121"/>
       <c r="J23" s="2">
         <v>0</v>
       </c>
@@ -4304,8 +4322,60 @@
     <row r="24" spans="2:16" x14ac:dyDescent="0.25">
       <c r="M24" s="3"/>
     </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>158</v>
+      </c>
+      <c r="D27" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>157</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="O21:O22"/>
+    <mergeCell ref="P21:P22"/>
+    <mergeCell ref="M20:P20"/>
+    <mergeCell ref="M21:M22"/>
+    <mergeCell ref="N21:N22"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="C6:C16"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="H20:L20"/>
+    <mergeCell ref="H21:I22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="K21:K22"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="K16:L16"/>
     <mergeCell ref="M4:N4"/>
@@ -4322,30 +4392,6 @@
     <mergeCell ref="B3:N3"/>
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="K9:L9"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="H20:L20"/>
-    <mergeCell ref="H21:I22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="K21:K22"/>
-    <mergeCell ref="C6:C16"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="L21:L22"/>
-    <mergeCell ref="O21:O22"/>
-    <mergeCell ref="P21:P22"/>
-    <mergeCell ref="M20:P20"/>
-    <mergeCell ref="M21:M22"/>
-    <mergeCell ref="N21:N22"/>
-    <mergeCell ref="K18:L18"/>
   </mergeCells>
   <phoneticPr fontId="28" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4355,18 +4401,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4514,18 +4560,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF0EB622-FDCF-4321-9FF5-C0B282D1670E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BC1EB47-4FFF-47F3-894F-DED91590EA19}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BC1EB47-4FFF-47F3-894F-DED91590EA19}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF0EB622-FDCF-4321-9FF5-C0B282D1670E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Docs/Lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/Docs/Lab02/Lab02_BBT_TCs_Form.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724B0AA4-A034-430C-B939-B65F45FF22CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C1EE37-7528-4596-A20E-F2F96349FA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="F01.BVA" sheetId="3" r:id="rId3"/>
     <sheet name="BBT-TCs" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -117,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="133">
   <si>
     <t>VVSS, Info Romana, 2024-2025</t>
   </si>
@@ -320,145 +320,18 @@
     <t>output data</t>
   </si>
   <si>
-    <t>titlu is String</t>
-  </si>
-  <si>
-    <t>titlu</t>
-  </si>
-  <si>
-    <t>regizor</t>
-  </si>
-  <si>
-    <t>an aparitie</t>
-  </si>
-  <si>
-    <t>actori</t>
-  </si>
-  <si>
-    <t>categorie</t>
-  </si>
-  <si>
-    <t>cuvinte cheie</t>
-  </si>
-  <si>
     <t>expected</t>
   </si>
   <si>
-    <t>titlu not String</t>
-  </si>
-  <si>
-    <t>1, 3, 5, 7, 9, …</t>
-  </si>
-  <si>
-    <t>"Movie Title"</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Director1, Director 2 Author2</t>
-  </si>
-  <si>
-    <t>Actor1, Actor2</t>
-  </si>
-  <si>
-    <t>Aventure</t>
-  </si>
-  <si>
-    <t>keyword1, keyword2</t>
-  </si>
-  <si>
     <t>2,3,2</t>
   </si>
   <si>
-    <t>record added</t>
-  </si>
-  <si>
-    <t>regizor is String</t>
-  </si>
-  <si>
     <t>…</t>
   </si>
   <si>
-    <t>...</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>regizor not String</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="30"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>, 3, 5, 7, 9</t>
-    </r>
-  </si>
-  <si>
-    <t>""</t>
-  </si>
-  <si>
-    <t>Error message-Empty title</t>
-  </si>
-  <si>
-    <t>an aparitie is number</t>
-  </si>
-  <si>
-    <t>..</t>
-  </si>
-  <si>
-    <t>an aparitie not number</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1, 3, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="49"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>, …</t>
-    </r>
-  </si>
-  <si>
-    <t>201q</t>
-  </si>
-  <si>
-    <t>Error message-? Compiler checked</t>
-  </si>
-  <si>
-    <t>an aparitie &gt; 1900</t>
-  </si>
-  <si>
-    <t>an aparitie not &gt; 1900</t>
-  </si>
-  <si>
-    <t>?</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -483,94 +356,7 @@
     <t>Executable</t>
   </si>
   <si>
-    <t>titlu is String, length in [1,255]</t>
-  </si>
-  <si>
-    <t>01. titlu = "", length = 0</t>
-  </si>
-  <si>
     <t>expected result</t>
-  </si>
-  <si>
-    <t>02. titlu = ?, length = -1</t>
-  </si>
-  <si>
-    <t>TC3_EC</t>
-  </si>
-  <si>
-    <t>03. titlu = "M", length = 1</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>04. titlu = "M…123", length = 255</t>
-  </si>
-  <si>
-    <t>"M"</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Director1, Director 2</t>
-  </si>
-  <si>
-    <t>Drama</t>
-  </si>
-  <si>
-    <t>05. titlu = "M…12", length = 254</t>
-  </si>
-  <si>
-    <t>"M…123"</t>
-  </si>
-  <si>
-    <t>06. titlu = "M…1234", length = 256</t>
-  </si>
-  <si>
-    <t>"M…12"</t>
-  </si>
-  <si>
-    <t>regizor is String, length in [1,255]</t>
-  </si>
-  <si>
-    <t>07. regizor = "", length = 0</t>
-  </si>
-  <si>
-    <t>"M…1234"</t>
-  </si>
-  <si>
-    <t>08. regizor = ?, length = -1</t>
-  </si>
-  <si>
-    <t>09. regizor = "D", length = 1</t>
-  </si>
-  <si>
-    <t>10. regizor = "D…123", length = 255</t>
-  </si>
-  <si>
-    <t>11. regizor = "D…12", length = 254</t>
-  </si>
-  <si>
-    <t>12. regizor = "D…1234", length = 256</t>
-  </si>
-  <si>
-    <t>an aparitie &gt;1900</t>
-  </si>
-  <si>
-    <t>13. an = 1960</t>
-  </si>
-  <si>
-    <t>14. an = 1959</t>
-  </si>
-  <si>
-    <t>15. an = 1961</t>
-  </si>
-  <si>
-    <t>16. an = max - 1</t>
-  </si>
-  <si>
-    <t>17. an = max + 1</t>
-  </si>
-  <si>
-    <t>18. an = max</t>
   </si>
   <si>
     <t>BBT TCs</t>
@@ -666,9 +452,6 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>not yet</t>
-  </si>
-  <si>
     <t>name</t>
   </si>
   <si>
@@ -769,13 +552,106 @@
   </si>
   <si>
     <t>price ∈ ℝ+</t>
+  </si>
+  <si>
+    <t>No Validation in Service</t>
+  </si>
+  <si>
+    <t>Validated in service</t>
+  </si>
+  <si>
+    <t>price ∉ ℝ+</t>
+  </si>
+  <si>
+    <t>inStock ∈ [min, max]</t>
+  </si>
+  <si>
+    <t>inStock ∉ [min, max]</t>
+  </si>
+  <si>
+    <t>Parte_de_test</t>
+  </si>
+  <si>
+    <t>Firma_de_test</t>
+  </si>
+  <si>
+    <t>parte1</t>
+  </si>
+  <si>
+    <t>company_a</t>
+  </si>
+  <si>
+    <t>company_b</t>
+  </si>
+  <si>
+    <t>2, 3</t>
+  </si>
+  <si>
+    <t>inStock  ∈ [min, max]</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>price=-0,000001</t>
+  </si>
+  <si>
+    <t>price=DOUBLE_MAX</t>
+  </si>
+  <si>
+    <t>price=0</t>
+  </si>
+  <si>
+    <t>price=1</t>
+  </si>
+  <si>
+    <t>price=DOUBLE_MAX-1</t>
+  </si>
+  <si>
+    <t>price=DOUBLE_MAX+1</t>
+  </si>
+  <si>
+    <t>inStock=min-1</t>
+  </si>
+  <si>
+    <t>inStock=min</t>
+  </si>
+  <si>
+    <t>inStock=min+1</t>
+  </si>
+  <si>
+    <t>inStock=max-1</t>
+  </si>
+  <si>
+    <t>inStock=max</t>
+  </si>
+  <si>
+    <t>inStock=max+1</t>
+  </si>
+  <si>
+    <t>TC1_EC, TC3_EC</t>
+  </si>
+  <si>
+    <t>TC1_EC, TC4_EC</t>
+  </si>
+  <si>
+    <t>TC2_EC, TC3_EC</t>
+  </si>
+  <si>
+    <t>Costea Gabriel-Antonio</t>
+  </si>
+  <si>
+    <t>Cozma Gheorghe Alexandru</t>
+  </si>
+  <si>
+    <t>Cretu Gabriel-Nicolae</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -818,25 +694,7 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="49"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color indexed="30"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color indexed="30"/>
       <name val="Calibri"/>
@@ -895,21 +753,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="8" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0070C0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -989,6 +832,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1460,9 +1309,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1470,79 +1319,68 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1550,40 +1388,55 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1607,67 +1460,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1682,127 +1505,140 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2112,37 +1948,37 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="22.5703125" customWidth="1"/>
-    <col min="9" max="9" width="32.85546875" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" customWidth="1"/>
-    <col min="12" max="12" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="22.5546875" customWidth="1"/>
+    <col min="9" max="9" width="32.88671875" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" customWidth="1"/>
+    <col min="12" max="12" width="12.109375" customWidth="1"/>
     <col min="14" max="14" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C1" s="52" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
       <c r="F1" s="54"/>
-      <c r="H1" s="47" t="s">
+      <c r="H1" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-    </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+    </row>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H2" s="55" t="s">
         <v>2</v>
       </c>
       <c r="I2" s="55"/>
       <c r="J2" s="55"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
         <v>3</v>
@@ -2151,62 +1987,74 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I4" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="J4" s="2">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="33"/>
+      <c r="I5" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="J5" s="2">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="28"/>
       <c r="H6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-    </row>
-    <row r="7" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="45" t="s">
+      <c r="I6" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J6" s="2">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B8" s="40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>12</v>
       </c>
@@ -2214,7 +2062,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>13</v>
       </c>
@@ -2222,7 +2070,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>14</v>
       </c>
@@ -2230,32 +2078,32 @@
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B18" s="45" t="s">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B18" s="40" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C20" s="43" t="s">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C20" s="38" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>19</v>
       </c>
@@ -2272,7 +2120,7 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>20</v>
       </c>
@@ -2289,8 +2137,8 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="44"/>
+    <row r="24" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="39"/>
       <c r="B24" s="51" t="s">
         <v>21</v>
       </c>
@@ -2307,8 +2155,36 @@
       <c r="M24" s="51"/>
       <c r="N24" s="51"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C26" s="46"/>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C26" s="41"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>98</v>
+      </c>
+      <c r="D31" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D32" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D33" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>97</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2326,25 +2202,25 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B1:Q22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:O22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.85546875" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.88671875" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="29.42578125" customWidth="1"/>
-    <col min="17" max="17" width="5" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5546875" customWidth="1"/>
+    <col min="10" max="10" width="13.21875" customWidth="1"/>
+    <col min="11" max="11" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21" customWidth="1"/>
+    <col min="15" max="15" width="29.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B1" s="52" t="s">
         <v>0</v>
       </c>
@@ -2352,7 +2228,7 @@
       <c r="D1" s="53"/>
       <c r="E1" s="54"/>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B3" s="59" t="s">
         <v>14</v>
       </c>
@@ -2362,7 +2238,7 @@
       <c r="F3" s="60"/>
       <c r="G3" s="61"/>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B5" s="62" t="s">
         <v>22</v>
       </c>
@@ -2380,507 +2256,411 @@
       <c r="M5" s="63"/>
       <c r="N5" s="63"/>
       <c r="O5" s="63"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-    </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="19" t="s">
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B6" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="16" t="s">
         <v>27</v>
       </c>
       <c r="G6" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="78" t="s">
+      <c r="H6" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="76" t="s">
+      <c r="I6" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="81"/>
-      <c r="K6" s="81"/>
-      <c r="L6" s="81"/>
-      <c r="M6" s="81"/>
-      <c r="N6" s="81"/>
-      <c r="O6" s="77"/>
-      <c r="P6" s="80" t="s">
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
+      <c r="M6" s="71"/>
+      <c r="N6" s="71"/>
+      <c r="O6" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="Q6" s="80"/>
-    </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="4">
         <v>1</v>
       </c>
       <c r="C7" s="56" t="s">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="E7" s="4"/>
       <c r="G7" s="65"/>
-      <c r="H7" s="79"/>
-      <c r="I7" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="J7" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="K7" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="M7" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="N7" s="76" t="s">
-        <v>38</v>
-      </c>
-      <c r="O7" s="77"/>
-      <c r="P7" s="76" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q7" s="77"/>
-    </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="H7" s="69"/>
+      <c r="I7" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="N7" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="O7" s="47" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B8" s="4">
         <v>2</v>
       </c>
       <c r="C8" s="56"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G8" s="16">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J8" s="2">
+        <v>10</v>
+      </c>
+      <c r="K8" s="2">
+        <v>30</v>
+      </c>
+      <c r="L8" s="2">
+        <v>20</v>
+      </c>
+      <c r="M8" s="2">
         <v>40</v>
       </c>
-      <c r="G8" s="19">
-        <v>1</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K8" s="2">
-        <v>2012</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="N8" s="74" t="s">
-        <v>46</v>
-      </c>
-      <c r="O8" s="75" t="s">
-        <v>47</v>
-      </c>
-      <c r="P8" s="74" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q8" s="75"/>
-    </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="N8" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="O8" s="113" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
         <v>3</v>
       </c>
       <c r="C9" s="56" t="s">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="E9" s="4"/>
-      <c r="G9" s="19">
+      <c r="G9" s="16">
         <v>2</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>50</v>
+      <c r="H9" s="2">
+        <v>2.2999999999999998</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N9" s="74" t="s">
-        <v>50</v>
-      </c>
-      <c r="O9" s="75" t="s">
-        <v>52</v>
-      </c>
-      <c r="P9" s="74" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q9" s="75"/>
-    </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="J9" s="2">
+        <v>-100</v>
+      </c>
+      <c r="K9" s="2">
+        <v>10</v>
+      </c>
+      <c r="L9" s="2">
+        <v>5</v>
+      </c>
+      <c r="M9" s="2">
+        <v>15</v>
+      </c>
+      <c r="N9" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="O9" s="114" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
         <v>4</v>
       </c>
       <c r="C10" s="56"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" s="32">
+        <v>106</v>
+      </c>
+      <c r="G10" s="16">
         <v>3</v>
       </c>
-      <c r="H10" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="K10" s="11">
-        <v>2012</v>
-      </c>
-      <c r="L10" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="N10" s="68" t="s">
-        <v>46</v>
-      </c>
-      <c r="O10" s="69"/>
-      <c r="P10" s="68" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q10" s="69"/>
-    </row>
-    <row r="11" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="4">
+      <c r="H10" s="115" t="s">
+        <v>112</v>
+      </c>
+      <c r="I10" s="116" t="s">
+        <v>107</v>
+      </c>
+      <c r="J10" s="116">
+        <v>-100</v>
+      </c>
+      <c r="K10" s="116">
+        <v>10</v>
+      </c>
+      <c r="L10" s="116">
         <v>5</v>
       </c>
-      <c r="C11" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M10" s="116">
+        <v>15</v>
+      </c>
+      <c r="N10" s="117" t="s">
+        <v>108</v>
+      </c>
+      <c r="O10" s="114" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="4"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="4"/>
       <c r="E11" s="4"/>
-      <c r="G11" s="32">
+      <c r="G11" s="16">
         <v>4</v>
       </c>
-      <c r="H11" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="L11" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="N11" s="68" t="s">
-        <v>50</v>
-      </c>
-      <c r="O11" s="69"/>
-      <c r="P11" s="68" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q11" s="69"/>
-    </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B12" s="4">
-        <v>6</v>
-      </c>
+      <c r="H11" s="116">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I11" s="116" t="s">
+        <v>107</v>
+      </c>
+      <c r="J11" s="116">
+        <v>-100</v>
+      </c>
+      <c r="K11" s="116">
+        <v>10</v>
+      </c>
+      <c r="L11" s="116">
+        <v>5</v>
+      </c>
+      <c r="M11" s="116">
+        <v>15</v>
+      </c>
+      <c r="N11" s="117" t="s">
+        <v>108</v>
+      </c>
+      <c r="O11" s="114" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B12" s="4"/>
       <c r="C12" s="56"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" s="10">
+      <c r="E12" s="4"/>
+      <c r="G12" s="16">
         <v>5</v>
       </c>
-      <c r="H12" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="O12" s="6"/>
-      <c r="P12" s="70" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q12" s="71"/>
-    </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B13" s="4">
-        <v>7</v>
-      </c>
-      <c r="C13" s="57" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>63</v>
-      </c>
+      <c r="H12" s="116">
+        <v>1.4</v>
+      </c>
+      <c r="I12" s="116" t="s">
+        <v>109</v>
+      </c>
+      <c r="J12" s="116">
+        <v>10</v>
+      </c>
+      <c r="K12" s="116">
+        <v>10</v>
+      </c>
+      <c r="L12" s="116">
+        <v>20</v>
+      </c>
+      <c r="M12" s="116">
+        <v>300</v>
+      </c>
+      <c r="N12" s="116" t="s">
+        <v>110</v>
+      </c>
+      <c r="O12" s="114" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B13" s="4"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="4"/>
       <c r="E13" s="4"/>
-      <c r="G13" s="10">
+      <c r="G13" s="16">
         <v>6</v>
       </c>
-      <c r="H13" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="N13" s="70" t="s">
-        <v>50</v>
-      </c>
-      <c r="O13" s="71"/>
-      <c r="P13" s="70" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q13" s="71"/>
-    </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B14" s="4">
-        <v>8</v>
-      </c>
+      <c r="H13" s="116">
+        <v>1.4</v>
+      </c>
+      <c r="I13" s="116" t="s">
+        <v>109</v>
+      </c>
+      <c r="J13" s="116">
+        <v>10</v>
+      </c>
+      <c r="K13" s="116">
+        <v>400</v>
+      </c>
+      <c r="L13" s="116">
+        <v>20</v>
+      </c>
+      <c r="M13" s="116">
+        <v>300</v>
+      </c>
+      <c r="N13" s="117" t="s">
+        <v>111</v>
+      </c>
+      <c r="O13" s="114" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B14" s="4"/>
       <c r="C14" s="58"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="G14" s="15">
+      <c r="E14" s="4"/>
+      <c r="G14" s="16">
         <v>7</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="116">
+        <v>1.3</v>
+      </c>
+      <c r="I14" s="116" t="s">
+        <v>107</v>
+      </c>
+      <c r="J14" s="116">
+        <v>100.5</v>
+      </c>
+      <c r="K14" s="116">
         <v>10</v>
       </c>
-      <c r="I14" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="J14" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="K14" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="L14" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="M14" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="N14" s="66" t="s">
-        <v>65</v>
-      </c>
-      <c r="O14" s="67"/>
-      <c r="P14" s="72"/>
-      <c r="Q14" s="73"/>
-    </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B15" s="4">
-        <v>9</v>
-      </c>
-      <c r="C15" s="56" t="s">
-        <v>50</v>
-      </c>
+      <c r="L14" s="116">
+        <v>5</v>
+      </c>
+      <c r="M14" s="116">
+        <v>15</v>
+      </c>
+      <c r="N14" s="118" t="s">
+        <v>108</v>
+      </c>
+      <c r="O14" s="113" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B15" s="4"/>
+      <c r="C15" s="56"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
-      <c r="G15" s="15">
-        <v>8</v>
-      </c>
-      <c r="H15" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="74"/>
-      <c r="O15" s="75"/>
-      <c r="P15" s="72"/>
-      <c r="Q15" s="73"/>
-    </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B16" s="4">
-        <v>10</v>
-      </c>
+      <c r="G15" s="12"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="46"/>
+      <c r="O15" s="114"/>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B16" s="4"/>
       <c r="C16" s="56"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="74"/>
-      <c r="O16" s="75"/>
-      <c r="P16" s="72"/>
-      <c r="Q16" s="73"/>
-    </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B17" s="4">
-        <v>11</v>
-      </c>
-      <c r="C17" s="56" t="s">
-        <v>50</v>
-      </c>
+      <c r="G16" s="12"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="46"/>
+      <c r="O16" s="114"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B17" s="4"/>
+      <c r="C17" s="56"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="74"/>
-      <c r="O17" s="75"/>
-      <c r="P17" s="72"/>
-      <c r="Q17" s="73"/>
-    </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B18" s="4">
-        <v>12</v>
-      </c>
+      <c r="G17" s="12"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="46"/>
+      <c r="O17" s="114"/>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B18" s="4"/>
       <c r="C18" s="56"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="74"/>
-      <c r="O18" s="75"/>
-      <c r="P18" s="72"/>
-      <c r="Q18" s="73"/>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B19" s="4">
-        <v>13</v>
-      </c>
-      <c r="C19" s="56" t="s">
-        <v>50</v>
-      </c>
+      <c r="G18" s="12"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="46"/>
+      <c r="O18" s="114"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B19" s="4"/>
+      <c r="C19" s="56"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
-      <c r="G19" s="19"/>
+      <c r="G19" s="16"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
-      <c r="N19" s="74"/>
-      <c r="O19" s="75"/>
-      <c r="P19" s="72"/>
-      <c r="Q19" s="73"/>
-    </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B20" s="4">
-        <v>14</v>
-      </c>
+      <c r="N19" s="46"/>
+      <c r="O19" s="114"/>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B20" s="4"/>
       <c r="C20" s="56"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>66</v>
-      </c>
-      <c r="F22" s="82"/>
-      <c r="G22" s="82"/>
+        <v>36</v>
+      </c>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
     </row>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="15">
     <mergeCell ref="F22:G22"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="N7:O7"/>
     <mergeCell ref="H6:H7"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="I6:O6"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="I6:N6"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="C7:C8"/>
@@ -2891,12 +2671,8 @@
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="G5:Q5"/>
+    <mergeCell ref="G5:O5"/>
     <mergeCell ref="G6:G7"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="P12:Q12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2907,28 +2683,28 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B1:R30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:AB30"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.77734375" customWidth="1"/>
+    <col min="4" max="4" width="30.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="5.5703125" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5703125" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.28515625" customWidth="1"/>
-    <col min="18" max="18" width="9.42578125" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" customWidth="1"/>
+    <col min="9" max="9" width="21.21875" customWidth="1"/>
+    <col min="10" max="10" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.88671875" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.109375" customWidth="1"/>
+    <col min="17" max="17" width="23.33203125" customWidth="1"/>
+    <col min="18" max="18" width="20.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B1" s="52" t="s">
         <v>0</v>
       </c>
@@ -2936,7 +2712,7 @@
       <c r="D1" s="53"/>
       <c r="E1" s="54"/>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B3" s="59" t="s">
         <v>14</v>
       </c>
@@ -2946,664 +2722,610 @@
       <c r="F3" s="60"/>
       <c r="G3" s="61"/>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B5" s="89" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
+    <row r="5" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B5" s="79" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="63" t="s">
-        <v>68</v>
-      </c>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="63"/>
-      <c r="L5" s="63"/>
-      <c r="M5" s="63"/>
-      <c r="N5" s="63"/>
-      <c r="O5" s="63"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-    </row>
-    <row r="6" spans="2:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G5" s="122" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="123"/>
+      <c r="I5" s="123"/>
+      <c r="J5" s="123"/>
+      <c r="K5" s="123"/>
+      <c r="L5" s="123"/>
+      <c r="M5" s="123"/>
+      <c r="N5" s="123"/>
+      <c r="O5" s="123"/>
+      <c r="P5" s="123"/>
+      <c r="Q5" s="124"/>
+      <c r="R5" s="122" t="s">
+        <v>38</v>
+      </c>
+      <c r="S5" s="123"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="123"/>
+      <c r="W5" s="123"/>
+      <c r="X5" s="123"/>
+      <c r="Y5" s="123"/>
+      <c r="Z5" s="123"/>
+      <c r="AA5" s="123"/>
+      <c r="AB5" s="124"/>
+    </row>
+    <row r="6" spans="2:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" s="7"/>
+        <v>37</v>
+      </c>
+      <c r="E6" s="6"/>
       <c r="G6" s="64" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="H6" s="64" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="I6" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J6" s="78" t="s">
-        <v>73</v>
-      </c>
-      <c r="K6" s="90" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="68" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" s="119" t="s">
         <v>30</v>
       </c>
-      <c r="L6" s="94"/>
-      <c r="M6" s="94"/>
-      <c r="N6" s="94"/>
-      <c r="O6" s="94"/>
-      <c r="P6" s="91"/>
-      <c r="Q6" s="90" t="s">
+      <c r="L6" s="120"/>
+      <c r="M6" s="120"/>
+      <c r="N6" s="120"/>
+      <c r="O6" s="120"/>
+      <c r="P6" s="121"/>
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="R6" s="91"/>
-    </row>
-    <row r="7" spans="2:18" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B7" s="57">
         <v>1</v>
       </c>
-      <c r="C7" s="84" t="s">
-        <v>74</v>
+      <c r="C7" s="74" t="s">
+        <v>101</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="G7" s="65"/>
       <c r="H7" s="65"/>
       <c r="I7" s="65"/>
-      <c r="J7" s="79"/>
-      <c r="K7" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="L7" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="M7" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="N7" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="O7" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="P7" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q7" s="76" t="s">
-        <v>76</v>
-      </c>
-      <c r="R7" s="77"/>
-    </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B8" s="83"/>
-      <c r="C8" s="85"/>
+      <c r="J7" s="69"/>
+      <c r="K7" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="N7" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="O7" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="P7" s="66" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q7" s="67"/>
+      <c r="R7" s="47" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B8" s="73"/>
+      <c r="C8" s="75"/>
       <c r="D8" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G8" s="16">
+        <v>1</v>
+      </c>
+      <c r="H8" s="10">
+        <v>8</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="K8" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="G8" s="19">
+      <c r="L8" s="7">
+        <v>10</v>
+      </c>
+      <c r="M8" s="45">
+        <v>5</v>
+      </c>
+      <c r="N8" s="45">
+        <v>5</v>
+      </c>
+      <c r="O8" s="45">
+        <v>15</v>
+      </c>
+      <c r="P8" s="84" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q8" s="85" t="s">
+        <v>83</v>
+      </c>
+      <c r="R8" s="45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B9" s="73"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G9" s="16">
+        <v>2</v>
+      </c>
+      <c r="H9" s="125">
+        <v>7</v>
+      </c>
+      <c r="I9" s="126" t="s">
+        <v>128</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="L9" s="7">
+        <v>10</v>
+      </c>
+      <c r="M9" s="45">
+        <v>4</v>
+      </c>
+      <c r="N9" s="45">
+        <v>5</v>
+      </c>
+      <c r="O9" s="45">
+        <v>15</v>
+      </c>
+      <c r="P9" s="84" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q9" s="85" t="s">
+        <v>84</v>
+      </c>
+      <c r="R9" s="45" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B10" s="73"/>
+      <c r="C10" s="75"/>
+      <c r="D10" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G10" s="16">
+        <v>3</v>
+      </c>
+      <c r="H10" s="10">
+        <v>5</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="M10" s="45">
+        <v>10</v>
+      </c>
+      <c r="N10" s="45">
+        <v>5</v>
+      </c>
+      <c r="O10" s="45">
+        <v>15</v>
+      </c>
+      <c r="P10" s="80" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q10" s="81" t="s">
+        <v>85</v>
+      </c>
+      <c r="R10" s="44" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="2:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="73"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G11" s="16">
+        <v>4</v>
+      </c>
+      <c r="H11" s="10">
         <v>1</v>
       </c>
-      <c r="H8" s="13">
-        <v>1</v>
-      </c>
-      <c r="I8" s="12" t="s">
+      <c r="I11" s="126" t="s">
+        <v>129</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="L11" s="7">
+        <v>-9.9999999999999995E-7</v>
+      </c>
+      <c r="M11" s="45">
+        <v>10</v>
+      </c>
+      <c r="N11" s="45">
+        <v>5</v>
+      </c>
+      <c r="O11" s="45">
+        <v>15</v>
+      </c>
+      <c r="P11" s="80" t="s">
         <v>78</v>
       </c>
-      <c r="J8" s="12"/>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="30"/>
-      <c r="P8" s="30"/>
-      <c r="Q8" s="92"/>
-      <c r="R8" s="93"/>
-    </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B9" s="83"/>
-      <c r="C9" s="85"/>
-      <c r="D9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9" s="15">
-        <v>2</v>
-      </c>
-      <c r="H9" s="16">
-        <v>2</v>
-      </c>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="K9" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="L9" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="M9" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="P9" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q9" s="70" t="s">
-        <v>62</v>
-      </c>
-      <c r="R9" s="71"/>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B10" s="83"/>
-      <c r="C10" s="85"/>
-      <c r="D10" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G10" s="19">
-        <v>3</v>
-      </c>
-      <c r="H10" s="13">
-        <v>3</v>
-      </c>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="29" t="s">
-        <v>82</v>
-      </c>
-      <c r="L10" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="M10" s="30">
-        <v>2010</v>
-      </c>
-      <c r="N10" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="O10" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="P10" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q10" s="92" t="s">
-        <v>48</v>
-      </c>
-      <c r="R10" s="93"/>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B11" s="83"/>
-      <c r="C11" s="85"/>
-      <c r="D11" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="G11" s="19">
-        <v>4</v>
-      </c>
-      <c r="H11" s="13">
-        <v>4</v>
-      </c>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="29" t="s">
+      <c r="Q11" s="81" t="s">
         <v>86</v>
       </c>
-      <c r="L11" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="M11" s="30">
-        <v>2010</v>
-      </c>
-      <c r="N11" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="O11" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="P11" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q11" s="92" t="s">
-        <v>48</v>
-      </c>
-      <c r="R11" s="93"/>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="R11" s="18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="2:28" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B12" s="58"/>
-      <c r="C12" s="86"/>
+      <c r="C12" s="76"/>
       <c r="D12" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="19">
+        <v>120</v>
+      </c>
+      <c r="G12" s="16">
         <v>5</v>
       </c>
-      <c r="H12" s="13">
-        <v>5</v>
-      </c>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="L12" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="M12" s="30">
-        <v>2010</v>
-      </c>
-      <c r="N12" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="O12" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="P12" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q12" s="92" t="s">
-        <v>48</v>
-      </c>
-      <c r="R12" s="93"/>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="H12" s="10"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="27"/>
+      <c r="O12" s="27"/>
+      <c r="P12" s="27"/>
+      <c r="Q12" s="49"/>
+    </row>
+    <row r="13" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B13" s="57">
         <v>2</v>
       </c>
       <c r="C13" s="57" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13" s="15">
+        <v>121</v>
+      </c>
+      <c r="G13" s="12">
         <v>6</v>
       </c>
-      <c r="H13" s="16">
-        <v>6</v>
-      </c>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="K13" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="M13" s="14">
-        <v>2010</v>
-      </c>
-      <c r="N13" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="O13" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="P13" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q13" s="70" t="s">
-        <v>62</v>
-      </c>
-      <c r="R13" s="71"/>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B14" s="83"/>
-      <c r="C14" s="83"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="48"/>
+    </row>
+    <row r="14" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
       <c r="D14" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G14" s="19">
+        <v>122</v>
+      </c>
+      <c r="G14" s="16">
         <v>7</v>
       </c>
-      <c r="H14" s="13">
-        <v>7</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="30"/>
-      <c r="O14" s="30"/>
-      <c r="P14" s="30"/>
-      <c r="Q14" s="92"/>
-      <c r="R14" s="93"/>
-    </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B15" s="83"/>
-      <c r="C15" s="83"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="27"/>
+      <c r="O14" s="27"/>
+      <c r="P14" s="27"/>
+      <c r="Q14" s="49"/>
+    </row>
+    <row r="15" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B15" s="73"/>
+      <c r="C15" s="73"/>
       <c r="D15" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G15" s="19">
+        <v>123</v>
+      </c>
+      <c r="G15" s="16">
         <v>8</v>
       </c>
-      <c r="H15" s="13">
-        <v>8</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="30"/>
-      <c r="O15" s="30"/>
-      <c r="P15" s="30"/>
-      <c r="Q15" s="92"/>
-      <c r="R15" s="93"/>
-    </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B16" s="83"/>
-      <c r="C16" s="83"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="27"/>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="49"/>
+    </row>
+    <row r="16" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B16" s="73"/>
+      <c r="C16" s="73"/>
       <c r="D16" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G16" s="19">
+        <v>124</v>
+      </c>
+      <c r="G16" s="16">
         <v>9</v>
       </c>
-      <c r="H16" s="13"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="30"/>
-      <c r="L16" s="30"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="30"/>
-      <c r="O16" s="30"/>
-      <c r="P16" s="30"/>
-      <c r="Q16" s="92"/>
-      <c r="R16" s="93"/>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B17" s="83"/>
-      <c r="C17" s="83"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27"/>
+      <c r="O16" s="27"/>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="49"/>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B17" s="73"/>
+      <c r="C17" s="73"/>
       <c r="D17" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G17" s="19">
+        <v>125</v>
+      </c>
+      <c r="G17" s="12">
         <v>10</v>
       </c>
-      <c r="H17" s="13"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="30"/>
-      <c r="L17" s="30"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="30"/>
-      <c r="O17" s="30"/>
-      <c r="P17" s="30"/>
-      <c r="Q17" s="92"/>
-      <c r="R17" s="93"/>
-    </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="H17" s="10"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="27"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="27"/>
+      <c r="N17" s="27"/>
+      <c r="O17" s="27"/>
+      <c r="P17" s="27"/>
+      <c r="Q17" s="49"/>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B18" s="58"/>
       <c r="C18" s="58"/>
       <c r="D18" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G18" s="19">
+        <v>126</v>
+      </c>
+      <c r="G18" s="16">
         <v>11</v>
       </c>
-      <c r="H18" s="13"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
-      <c r="N18" s="30"/>
-      <c r="O18" s="30"/>
-      <c r="P18" s="30"/>
-      <c r="Q18" s="92"/>
-      <c r="R18" s="93"/>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="H18" s="10"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="27"/>
+      <c r="L18" s="27"/>
+      <c r="M18" s="27"/>
+      <c r="N18" s="27"/>
+      <c r="O18" s="27"/>
+      <c r="P18" s="27"/>
+      <c r="Q18" s="49"/>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B19" s="57">
         <v>3</v>
       </c>
-      <c r="C19" s="84" t="s">
-        <v>97</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G19" s="19">
+      <c r="C19" s="74"/>
+      <c r="D19" s="2"/>
+      <c r="G19" s="16">
         <v>12</v>
       </c>
-      <c r="H19" s="13"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="30"/>
-      <c r="L19" s="30"/>
-      <c r="M19" s="30"/>
-      <c r="N19" s="30"/>
-      <c r="O19" s="30"/>
-      <c r="P19" s="30"/>
-      <c r="Q19" s="92"/>
-      <c r="R19" s="93"/>
-    </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B20" s="83"/>
-      <c r="C20" s="85"/>
-      <c r="D20" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G20" s="19">
+      <c r="H19" s="10"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="27"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="27"/>
+      <c r="O19" s="27"/>
+      <c r="P19" s="27"/>
+      <c r="Q19" s="49"/>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B20" s="73"/>
+      <c r="C20" s="75"/>
+      <c r="D20" s="2"/>
+      <c r="G20" s="16">
         <v>13</v>
       </c>
-      <c r="H20" s="13"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="30"/>
-      <c r="P20" s="30"/>
-      <c r="Q20" s="92"/>
-      <c r="R20" s="93"/>
-    </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B21" s="83"/>
-      <c r="C21" s="85"/>
-      <c r="D21" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G21" s="19">
+      <c r="H20" s="10"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="27"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="27"/>
+      <c r="P20" s="27"/>
+      <c r="Q20" s="49"/>
+    </row>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B21" s="73"/>
+      <c r="C21" s="75"/>
+      <c r="D21" s="2"/>
+      <c r="G21" s="12">
         <v>14</v>
       </c>
-      <c r="H21" s="13"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="30"/>
-      <c r="L21" s="30"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="30"/>
-      <c r="O21" s="30"/>
-      <c r="P21" s="30"/>
-      <c r="Q21" s="92"/>
-      <c r="R21" s="93"/>
-    </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B22" s="83"/>
-      <c r="C22" s="85"/>
-      <c r="D22" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="G22" s="19">
+      <c r="H21" s="10"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="27"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="27"/>
+      <c r="N21" s="27"/>
+      <c r="O21" s="27"/>
+      <c r="P21" s="27"/>
+      <c r="Q21" s="49"/>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B22" s="73"/>
+      <c r="C22" s="75"/>
+      <c r="D22" s="2"/>
+      <c r="G22" s="16">
         <v>15</v>
       </c>
-      <c r="H22" s="13"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="30"/>
-      <c r="L22" s="30"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="30"/>
-      <c r="O22" s="30"/>
-      <c r="P22" s="30"/>
-      <c r="Q22" s="92"/>
-      <c r="R22" s="93"/>
-    </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B23" s="83"/>
-      <c r="C23" s="85"/>
-      <c r="D23" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G23" s="19">
+      <c r="H22" s="10"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="27"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="27"/>
+      <c r="N22" s="27"/>
+      <c r="O22" s="27"/>
+      <c r="P22" s="27"/>
+      <c r="Q22" s="49"/>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B23" s="73"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="2"/>
+      <c r="G23" s="16">
         <v>16</v>
       </c>
-      <c r="H23" s="13"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="30"/>
-      <c r="P23" s="30"/>
-      <c r="Q23" s="92"/>
-      <c r="R23" s="93"/>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="H23" s="10"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="27"/>
+      <c r="O23" s="27"/>
+      <c r="P23" s="27"/>
+      <c r="Q23" s="49"/>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B24" s="58"/>
-      <c r="C24" s="86"/>
-      <c r="D24" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G24" s="19">
+      <c r="C24" s="76"/>
+      <c r="D24" s="2"/>
+      <c r="G24" s="16">
         <v>17</v>
       </c>
-      <c r="H24" s="13"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="30"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="30"/>
-      <c r="O24" s="30"/>
-      <c r="P24" s="30"/>
-      <c r="Q24" s="92"/>
-      <c r="R24" s="93"/>
-    </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="H24" s="10"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="27"/>
+      <c r="N24" s="27"/>
+      <c r="O24" s="27"/>
+      <c r="P24" s="27"/>
+      <c r="Q24" s="49"/>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B25" s="57">
         <v>4</v>
       </c>
-      <c r="C25" s="84" t="s">
-        <v>50</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G25" s="19">
+      <c r="C25" s="74"/>
+      <c r="D25" s="2"/>
+      <c r="G25" s="12">
         <v>18</v>
       </c>
-      <c r="H25" s="13"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="30"/>
-      <c r="L25" s="30"/>
-      <c r="M25" s="30"/>
-      <c r="N25" s="30"/>
-      <c r="O25" s="30"/>
-      <c r="P25" s="30"/>
-      <c r="Q25" s="92"/>
-      <c r="R25" s="93"/>
-    </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B26" s="83"/>
-      <c r="C26" s="85"/>
-      <c r="D26" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B27" s="83"/>
-      <c r="C27" s="85"/>
-      <c r="D27" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B28" s="83"/>
-      <c r="C28" s="85"/>
-      <c r="D28" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G28" s="82"/>
-      <c r="H28" s="82"/>
-      <c r="I28" s="88"/>
-      <c r="J28" s="88"/>
-      <c r="K28" s="88"/>
-      <c r="L28" s="88"/>
-      <c r="M28" s="88"/>
-      <c r="N28" s="39"/>
-    </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B29" s="83"/>
-      <c r="C29" s="85"/>
-      <c r="D29" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I29" s="87"/>
-      <c r="J29" s="87"/>
-      <c r="K29" s="87"/>
-      <c r="L29" s="87"/>
-      <c r="M29" s="87"/>
-      <c r="N29" s="40"/>
-    </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="H25" s="10"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="27"/>
+      <c r="L25" s="27"/>
+      <c r="M25" s="27"/>
+      <c r="N25" s="27"/>
+      <c r="O25" s="27"/>
+      <c r="P25" s="27"/>
+      <c r="Q25" s="49"/>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B26" s="73"/>
+      <c r="C26" s="75"/>
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B27" s="73"/>
+      <c r="C27" s="75"/>
+      <c r="D27" s="2"/>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B28" s="73"/>
+      <c r="C28" s="75"/>
+      <c r="D28" s="2"/>
+      <c r="G28" s="72"/>
+      <c r="H28" s="72"/>
+      <c r="I28" s="78"/>
+      <c r="J28" s="78"/>
+      <c r="K28" s="78"/>
+      <c r="L28" s="78"/>
+      <c r="M28" s="78"/>
+      <c r="N28" s="34"/>
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B29" s="73"/>
+      <c r="C29" s="75"/>
+      <c r="D29" s="2"/>
+      <c r="I29" s="77"/>
+      <c r="J29" s="77"/>
+      <c r="K29" s="77"/>
+      <c r="L29" s="77"/>
+      <c r="M29" s="77"/>
+      <c r="N29" s="35"/>
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B30" s="58"/>
-      <c r="C30" s="86"/>
-      <c r="D30" s="2" t="s">
-        <v>50</v>
-      </c>
+      <c r="C30" s="76"/>
+      <c r="D30" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="K6:P6"/>
-    <mergeCell ref="Q10:R10"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="Q12:R12"/>
+  <mergeCells count="25">
+    <mergeCell ref="R5:AB5"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="P7:Q7"/>
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="I28:M28"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="Q6:R6"/>
     <mergeCell ref="H6:H7"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="Q9:R9"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="I6:I7"/>
@@ -3617,9 +3339,8 @@
     <mergeCell ref="C19:C24"/>
     <mergeCell ref="B19:B24"/>
     <mergeCell ref="I29:M29"/>
-    <mergeCell ref="G5:R5"/>
+    <mergeCell ref="G5:Q5"/>
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="Q7:R7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3632,20 +3353,20 @@
   <sheetPr>
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="B1:P31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:P24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="6" width="14.5703125" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" customWidth="1"/>
-    <col min="13" max="13" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" customWidth="1"/>
+    <col min="7" max="7" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" customWidth="1"/>
+    <col min="9" max="9" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.88671875" customWidth="1"/>
+    <col min="13" max="13" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B1" s="52" t="s">
         <v>0</v>
       </c>
@@ -3653,702 +3374,678 @@
       <c r="D1" s="53"/>
       <c r="E1" s="54"/>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="104" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="104"/>
-      <c r="I3" s="104"/>
-      <c r="J3" s="104"/>
-      <c r="K3" s="104"/>
-      <c r="L3" s="104"/>
-      <c r="M3" s="104"/>
-      <c r="N3" s="104"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B3" s="89" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
+      <c r="K3" s="89"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="89"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="102" t="s">
-        <v>106</v>
-      </c>
-      <c r="D4" s="118" t="s">
-        <v>107</v>
-      </c>
-      <c r="E4" s="78" t="s">
-        <v>108</v>
-      </c>
-      <c r="F4" s="76" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="87" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="103" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="81"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="81"/>
-      <c r="K4" s="81"/>
-      <c r="L4" s="77"/>
-      <c r="M4" s="80" t="s">
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="N4" s="80"/>
-    </row>
-    <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="117"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="G5" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="H5" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="I5" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="J5" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="K5" s="97" t="s">
-        <v>133</v>
-      </c>
-      <c r="L5" s="98"/>
-      <c r="M5" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5" s="22" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="20">
+      <c r="N4" s="70"/>
+    </row>
+    <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="102"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="86"/>
+      <c r="F5" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="K5" s="82" t="s">
+        <v>73</v>
+      </c>
+      <c r="L5" s="83"/>
+      <c r="M5" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="N5" s="19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="17">
         <v>1</v>
       </c>
-      <c r="C6" s="115" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="E6" s="20" t="s">
+      <c r="C6" s="100" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="G6" s="25">
+      <c r="E6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="22">
         <v>10</v>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="22">
         <v>30</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="22">
         <v>20</v>
       </c>
-      <c r="J6" s="25">
+      <c r="J6" s="22">
         <v>40</v>
       </c>
-      <c r="K6" s="95" t="s">
-        <v>138</v>
-      </c>
-      <c r="L6" s="96" t="s">
-        <v>47</v>
-      </c>
-      <c r="M6" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="N6" s="20" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B7" s="9">
+      <c r="K6" s="80" t="s">
+        <v>78</v>
+      </c>
+      <c r="L6" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="N6" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B7" s="8">
         <f>B6+1</f>
         <v>2</v>
       </c>
-      <c r="C7" s="115"/>
-      <c r="D7" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="F7" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="G7" s="8">
+      <c r="C7" s="100"/>
+      <c r="D7" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="7">
         <v>-100</v>
       </c>
-      <c r="H7" s="50">
+      <c r="H7" s="45">
         <v>10</v>
       </c>
-      <c r="I7" s="50">
+      <c r="I7" s="45">
         <v>5</v>
       </c>
-      <c r="J7" s="50">
+      <c r="J7" s="45">
         <v>15</v>
       </c>
-      <c r="K7" s="99" t="s">
-        <v>138</v>
-      </c>
-      <c r="L7" s="100" t="s">
-        <v>139</v>
-      </c>
-      <c r="M7" s="50" t="s">
-        <v>150</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B8" s="9">
+      <c r="K7" s="84" t="s">
+        <v>78</v>
+      </c>
+      <c r="L7" s="85" t="s">
+        <v>79</v>
+      </c>
+      <c r="M7" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B8" s="8">
         <v>3</v>
       </c>
-      <c r="C8" s="115"/>
-      <c r="D8" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="G8" s="8">
+      <c r="C8" s="100"/>
+      <c r="D8" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="7">
         <v>-100</v>
       </c>
-      <c r="H8" s="50">
+      <c r="H8" s="45">
         <v>10</v>
       </c>
-      <c r="I8" s="50">
+      <c r="I8" s="45">
         <v>5</v>
       </c>
-      <c r="J8" s="50">
+      <c r="J8" s="45">
         <v>15</v>
       </c>
-      <c r="K8" s="99" t="s">
-        <v>138</v>
-      </c>
-      <c r="L8" s="100" t="s">
-        <v>140</v>
-      </c>
-      <c r="M8" s="50" t="s">
-        <v>150</v>
-      </c>
-      <c r="N8" s="20" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B9" s="9">
+      <c r="K8" s="84" t="s">
+        <v>78</v>
+      </c>
+      <c r="L8" s="85" t="s">
+        <v>80</v>
+      </c>
+      <c r="M8" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B9" s="8">
         <v>4</v>
       </c>
-      <c r="C9" s="115"/>
-      <c r="D9" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="G9" s="8">
+      <c r="C9" s="100"/>
+      <c r="D9" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="7">
         <v>-100</v>
       </c>
-      <c r="H9" s="50">
+      <c r="H9" s="45">
         <v>10</v>
       </c>
-      <c r="I9" s="50">
+      <c r="I9" s="45">
         <v>5</v>
       </c>
-      <c r="J9" s="50">
+      <c r="J9" s="45">
         <v>15</v>
       </c>
-      <c r="K9" s="99" t="s">
-        <v>138</v>
-      </c>
-      <c r="L9" s="100" t="s">
-        <v>141</v>
-      </c>
-      <c r="M9" s="50" t="s">
-        <v>150</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B10" s="20">
+      <c r="K9" s="84" t="s">
+        <v>78</v>
+      </c>
+      <c r="L9" s="85" t="s">
+        <v>81</v>
+      </c>
+      <c r="M9" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B10" s="17">
         <v>5</v>
       </c>
-      <c r="C10" s="115"/>
-      <c r="D10" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="G10" s="8">
+      <c r="C10" s="100"/>
+      <c r="D10" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" s="7">
         <v>10</v>
       </c>
-      <c r="H10" s="50">
+      <c r="H10" s="45">
         <v>10</v>
       </c>
-      <c r="I10" s="50">
+      <c r="I10" s="45">
         <v>20</v>
       </c>
-      <c r="J10" s="50">
+      <c r="J10" s="45">
         <v>300</v>
       </c>
-      <c r="K10" s="99" t="s">
-        <v>152</v>
-      </c>
-      <c r="L10" s="100" t="s">
-        <v>140</v>
-      </c>
-      <c r="M10" s="50" t="s">
-        <v>150</v>
-      </c>
-      <c r="N10" s="20" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B11" s="9">
+      <c r="K10" s="84" t="s">
+        <v>92</v>
+      </c>
+      <c r="L10" s="85" t="s">
+        <v>80</v>
+      </c>
+      <c r="M10" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B11" s="8">
         <v>6</v>
       </c>
-      <c r="C11" s="115"/>
-      <c r="D11" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="F11" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="G11" s="8">
+      <c r="C11" s="100"/>
+      <c r="D11" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="G11" s="7">
         <v>10</v>
       </c>
-      <c r="H11" s="50">
+      <c r="H11" s="45">
         <v>400</v>
       </c>
-      <c r="I11" s="50">
+      <c r="I11" s="45">
         <v>20</v>
       </c>
-      <c r="J11" s="50">
+      <c r="J11" s="45">
         <v>300</v>
       </c>
-      <c r="K11" s="99" t="s">
-        <v>153</v>
-      </c>
-      <c r="L11" s="100" t="s">
-        <v>141</v>
-      </c>
-      <c r="M11" s="50" t="s">
-        <v>150</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B12" s="9">
+      <c r="K11" s="84" t="s">
+        <v>93</v>
+      </c>
+      <c r="L11" s="85" t="s">
+        <v>81</v>
+      </c>
+      <c r="M11" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B12" s="8">
         <v>7</v>
       </c>
-      <c r="C12" s="115"/>
-      <c r="D12" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="G12" s="8">
+      <c r="C12" s="100"/>
+      <c r="D12" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="7">
         <v>100.5</v>
       </c>
-      <c r="H12" s="50">
+      <c r="H12" s="45">
         <v>10</v>
       </c>
-      <c r="I12" s="50">
+      <c r="I12" s="45">
         <v>5</v>
       </c>
-      <c r="J12" s="50">
+      <c r="J12" s="45">
         <v>15</v>
       </c>
-      <c r="K12" s="99" t="s">
-        <v>138</v>
-      </c>
-      <c r="L12" s="100" t="s">
-        <v>142</v>
-      </c>
-      <c r="M12" s="50" t="s">
-        <v>147</v>
-      </c>
-      <c r="N12" s="20" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B13" s="9">
+      <c r="K12" s="84" t="s">
+        <v>78</v>
+      </c>
+      <c r="L12" s="85" t="s">
+        <v>82</v>
+      </c>
+      <c r="M12" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B13" s="8">
         <v>8</v>
       </c>
-      <c r="C13" s="115"/>
-      <c r="D13" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="F13" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="G13" s="8">
+      <c r="C13" s="100"/>
+      <c r="D13" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="7">
         <v>10</v>
       </c>
-      <c r="H13" s="50">
+      <c r="H13" s="45">
         <v>5</v>
       </c>
-      <c r="I13" s="50">
+      <c r="I13" s="45">
         <v>5</v>
       </c>
-      <c r="J13" s="50">
+      <c r="J13" s="45">
         <v>15</v>
       </c>
-      <c r="K13" s="99" t="s">
-        <v>138</v>
-      </c>
-      <c r="L13" s="100" t="s">
-        <v>143</v>
-      </c>
-      <c r="M13" s="50" t="s">
-        <v>147</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="20">
+      <c r="K13" s="84" t="s">
+        <v>78</v>
+      </c>
+      <c r="L13" s="85" t="s">
+        <v>83</v>
+      </c>
+      <c r="M13" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B14" s="17">
         <v>9</v>
       </c>
-      <c r="C14" s="115"/>
-      <c r="D14" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="G14" s="8">
+      <c r="C14" s="100"/>
+      <c r="D14" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="7">
         <v>10</v>
       </c>
-      <c r="H14" s="50">
+      <c r="H14" s="45">
         <v>4</v>
       </c>
-      <c r="I14" s="50">
+      <c r="I14" s="45">
         <v>5</v>
       </c>
-      <c r="J14" s="50">
+      <c r="J14" s="45">
         <v>15</v>
       </c>
-      <c r="K14" s="99" t="s">
-        <v>138</v>
-      </c>
-      <c r="L14" s="100" t="s">
-        <v>144</v>
-      </c>
-      <c r="M14" s="50" t="s">
-        <v>150</v>
-      </c>
-      <c r="N14" s="20" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="20">
+      <c r="K14" s="84" t="s">
+        <v>78</v>
+      </c>
+      <c r="L14" s="85" t="s">
+        <v>84</v>
+      </c>
+      <c r="M14" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B15" s="17">
         <v>10</v>
       </c>
-      <c r="C15" s="115"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="F15" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="H15" s="50">
+      <c r="C15" s="100"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="H15" s="45">
         <v>10</v>
       </c>
-      <c r="I15" s="50">
+      <c r="I15" s="45">
         <v>5</v>
       </c>
-      <c r="J15" s="50">
+      <c r="J15" s="45">
         <v>15</v>
       </c>
-      <c r="K15" s="95" t="s">
-        <v>138</v>
-      </c>
-      <c r="L15" s="96" t="s">
-        <v>145</v>
-      </c>
-      <c r="M15" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="N15" s="9" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="16" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="9">
+      <c r="K15" s="80" t="s">
+        <v>78</v>
+      </c>
+      <c r="L15" s="81" t="s">
+        <v>85</v>
+      </c>
+      <c r="M15" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="N15" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="8">
         <v>11</v>
       </c>
-      <c r="C16" s="116"/>
-      <c r="D16" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="G16" s="8">
+      <c r="C16" s="101"/>
+      <c r="D16" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="7">
         <v>-9.9999999999999995E-7</v>
       </c>
-      <c r="H16" s="50">
+      <c r="H16" s="45">
         <v>10</v>
       </c>
-      <c r="I16" s="50">
+      <c r="I16" s="45">
         <v>5</v>
       </c>
-      <c r="J16" s="50">
+      <c r="J16" s="45">
         <v>15</v>
       </c>
-      <c r="K16" s="95" t="s">
-        <v>138</v>
-      </c>
-      <c r="L16" s="96" t="s">
-        <v>146</v>
-      </c>
-      <c r="M16" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="N16" s="20" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="17" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-    </row>
-    <row r="18" spans="2:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="C18" s="23"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="23"/>
+      <c r="K16" s="80" t="s">
+        <v>78</v>
+      </c>
+      <c r="L16" s="81" t="s">
+        <v>86</v>
+      </c>
+      <c r="M16" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+    </row>
+    <row r="18" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="20"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="20"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
-      <c r="K18" s="127"/>
-      <c r="L18" s="127"/>
+      <c r="K18" s="112"/>
+      <c r="L18" s="112"/>
       <c r="M18" s="5"/>
     </row>
-    <row r="19" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="M19" s="5"/>
     </row>
-    <row r="20" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C20" s="106" t="s">
-        <v>117</v>
-      </c>
-      <c r="D20" s="107"/>
-      <c r="E20" s="107"/>
-      <c r="F20" s="108"/>
-      <c r="G20" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="H20" s="106" t="s">
-        <v>119</v>
-      </c>
-      <c r="I20" s="109"/>
-      <c r="J20" s="107"/>
-      <c r="K20" s="107"/>
-      <c r="L20" s="108"/>
-      <c r="M20" s="106" t="s">
-        <v>120</v>
-      </c>
-      <c r="N20" s="109"/>
-      <c r="O20" s="107"/>
-      <c r="P20" s="108"/>
-    </row>
-    <row r="21" spans="2:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="122" t="s">
-        <v>106</v>
-      </c>
-      <c r="C21" s="123" t="s">
-        <v>121</v>
-      </c>
-      <c r="D21" s="105" t="s">
-        <v>122</v>
-      </c>
-      <c r="E21" s="105" t="s">
-        <v>123</v>
-      </c>
-      <c r="F21" s="124" t="s">
-        <v>124</v>
-      </c>
-      <c r="G21" s="114" t="s">
-        <v>125</v>
-      </c>
-      <c r="H21" s="110" t="s">
-        <v>126</v>
-      </c>
-      <c r="I21" s="111"/>
-      <c r="J21" s="105" t="s">
-        <v>121</v>
-      </c>
-      <c r="K21" s="105" t="s">
-        <v>122</v>
-      </c>
-      <c r="L21" s="124" t="s">
-        <v>123</v>
-      </c>
-      <c r="M21" s="125" t="s">
-        <v>126</v>
-      </c>
-      <c r="N21" s="105" t="s">
-        <v>121</v>
-      </c>
-      <c r="O21" s="105" t="s">
-        <v>122</v>
-      </c>
-      <c r="P21" s="124" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B22" s="122"/>
-      <c r="C22" s="123"/>
-      <c r="D22" s="105"/>
-      <c r="E22" s="105"/>
-      <c r="F22" s="124"/>
-      <c r="G22" s="114"/>
-      <c r="H22" s="112"/>
-      <c r="I22" s="113"/>
-      <c r="J22" s="105"/>
-      <c r="K22" s="105"/>
-      <c r="L22" s="124"/>
-      <c r="M22" s="126"/>
-      <c r="N22" s="105"/>
-      <c r="O22" s="105"/>
-      <c r="P22" s="124"/>
-    </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B23" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="C23" s="34">
+    <row r="20" spans="2:16" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="C20" s="91" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="92"/>
+      <c r="E20" s="92"/>
+      <c r="F20" s="93"/>
+      <c r="G20" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" s="91" t="s">
+        <v>60</v>
+      </c>
+      <c r="I20" s="94"/>
+      <c r="J20" s="92"/>
+      <c r="K20" s="92"/>
+      <c r="L20" s="93"/>
+      <c r="M20" s="91" t="s">
+        <v>61</v>
+      </c>
+      <c r="N20" s="94"/>
+      <c r="O20" s="92"/>
+      <c r="P20" s="93"/>
+    </row>
+    <row r="21" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="107" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="108" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="90" t="s">
+        <v>63</v>
+      </c>
+      <c r="E21" s="90" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="109" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21" s="99" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" s="95" t="s">
+        <v>67</v>
+      </c>
+      <c r="I21" s="96"/>
+      <c r="J21" s="90" t="s">
+        <v>62</v>
+      </c>
+      <c r="K21" s="90" t="s">
+        <v>63</v>
+      </c>
+      <c r="L21" s="109" t="s">
+        <v>64</v>
+      </c>
+      <c r="M21" s="110" t="s">
+        <v>67</v>
+      </c>
+      <c r="N21" s="90" t="s">
+        <v>62</v>
+      </c>
+      <c r="O21" s="90" t="s">
+        <v>63</v>
+      </c>
+      <c r="P21" s="109" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B22" s="107"/>
+      <c r="C22" s="108"/>
+      <c r="D22" s="90"/>
+      <c r="E22" s="90"/>
+      <c r="F22" s="109"/>
+      <c r="G22" s="99"/>
+      <c r="H22" s="97"/>
+      <c r="I22" s="98"/>
+      <c r="J22" s="90"/>
+      <c r="K22" s="90"/>
+      <c r="L22" s="109"/>
+      <c r="M22" s="111"/>
+      <c r="N22" s="90"/>
+      <c r="O22" s="90"/>
+      <c r="P22" s="109"/>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B23" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="29">
         <v>11</v>
       </c>
-      <c r="D23" s="36">
+      <c r="D23" s="31">
         <v>4</v>
       </c>
-      <c r="E23" s="36">
+      <c r="E23" s="31">
         <v>7</v>
       </c>
-      <c r="F23" s="37"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="120" t="s">
-        <v>127</v>
-      </c>
-      <c r="I23" s="121"/>
+      <c r="F23" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="G23" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="H23" s="105">
+        <v>7</v>
+      </c>
+      <c r="I23" s="106"/>
       <c r="J23" s="2">
+        <v>11</v>
+      </c>
+      <c r="K23" s="31">
+        <v>11</v>
+      </c>
+      <c r="L23" s="32">
         <v>0</v>
       </c>
-      <c r="K23" s="36">
+      <c r="M23" s="36">
+        <v>4</v>
+      </c>
+      <c r="N23" s="2">
+        <v>11</v>
+      </c>
+      <c r="O23" s="31">
+        <v>11</v>
+      </c>
+      <c r="P23" s="32">
         <v>0</v>
       </c>
-      <c r="L23" s="37">
-        <v>0</v>
-      </c>
-      <c r="M23" s="41" t="s">
-        <v>127</v>
-      </c>
-      <c r="N23" s="2">
-        <v>0</v>
-      </c>
-      <c r="O23" s="36">
-        <v>0</v>
-      </c>
-      <c r="P23" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
       <c r="M24" s="3"/>
-    </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>158</v>
-      </c>
-      <c r="D27" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D28" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D29" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>157</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="40">
@@ -4393,7 +4090,7 @@
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="K9:L9"/>
   </mergeCells>
-  <phoneticPr fontId="28" type="noConversion"/>
+  <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
